--- a/resources/OneStream Marketing Spend Pull.xlsx
+++ b/resources/OneStream Marketing Spend Pull.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian.schlesinger\Documents\GitHub\fin-mtkg-data-v2\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A85789-D30F-4D9A-9993-3F63191AA128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A32AF1-AB98-42F1-B845-44FDBF1AB24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" xr2:uid="{2334A0E9-8245-42B0-9552-867C20907550}"/>
+    <workbookView xWindow="-165" yWindow="-165" windowWidth="38730" windowHeight="21210" activeTab="2" xr2:uid="{2334A0E9-8245-42B0-9552-867C20907550}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,14 +35,14 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version warnBelowVersion="2" setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2975" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="214">
   <si>
     <t>UD2</t>
   </si>
@@ -298,15 +298,403 @@
   <si>
     <t>not completed because of the SACADV stuff!!!</t>
   </si>
+  <si>
+    <t>111-170SACADV000000</t>
+  </si>
+  <si>
+    <t>111-170SACADV000002</t>
+  </si>
+  <si>
+    <t>111-170SACADV000001</t>
+  </si>
+  <si>
+    <t>113-100SUBAAD</t>
+  </si>
+  <si>
+    <t>113-101SUBAAD</t>
+  </si>
+  <si>
+    <t>113-102SUBAAD</t>
+  </si>
+  <si>
+    <t>113-103SUBAAD</t>
+  </si>
+  <si>
+    <t>113-120SUBAAD</t>
+  </si>
+  <si>
+    <t>113-125SUBAAD</t>
+  </si>
+  <si>
+    <t>113-130SUBAAD</t>
+  </si>
+  <si>
+    <t>113-131SUBAAD</t>
+  </si>
+  <si>
+    <t>113-135SUBAAD</t>
+  </si>
+  <si>
+    <t>113-115SUBAAD</t>
+  </si>
+  <si>
+    <t>113-132SUBAAD</t>
+  </si>
+  <si>
+    <t>111-443SUBAAD</t>
+  </si>
+  <si>
+    <t>111-444SUBAAD</t>
+  </si>
+  <si>
+    <t>291-307SUBAAD</t>
+  </si>
+  <si>
+    <t>213-445SUBAAD</t>
+  </si>
+  <si>
+    <t>213-100SUBAAD</t>
+  </si>
+  <si>
+    <t>213-120SUBAAD</t>
+  </si>
+  <si>
+    <t>111-449SUBAAD</t>
+  </si>
+  <si>
+    <t>111-130SUBAAD</t>
+  </si>
+  <si>
+    <t>213-130SUBAAD</t>
+  </si>
+  <si>
+    <t>111-450SUBAAD</t>
+  </si>
+  <si>
+    <t>113-104SUBAAD</t>
+  </si>
+  <si>
+    <t>113-123SUBAAD</t>
+  </si>
+  <si>
+    <t>900-950SUBAAD</t>
+  </si>
+  <si>
+    <t>905-950SUBAAD</t>
+  </si>
+  <si>
+    <t>186-520SUBAAD</t>
+  </si>
+  <si>
+    <t>111-380SUBAAD</t>
+  </si>
+  <si>
+    <t>290-380SUBAAD</t>
+  </si>
+  <si>
+    <t>111-105SUBAAD</t>
+  </si>
+  <si>
+    <t>111-304SUBAAD</t>
+  </si>
+  <si>
+    <t>113-501SUBAAD</t>
+  </si>
+  <si>
+    <t>113-500SUBAAD</t>
+  </si>
+  <si>
+    <t>113-525SUBAAD</t>
+  </si>
+  <si>
+    <t>IT-113 SUBAAD</t>
+  </si>
+  <si>
+    <t>113-110SUBAAD</t>
+  </si>
+  <si>
+    <t>111-175SUBAAD</t>
+  </si>
+  <si>
+    <t>113-513SUBAAD</t>
+  </si>
+  <si>
+    <t>113-519SUBAAD</t>
+  </si>
+  <si>
+    <t>113-515SUBAAD</t>
+  </si>
+  <si>
+    <t>113-510SUBAAD</t>
+  </si>
+  <si>
+    <t>113-518SUBAAD</t>
+  </si>
+  <si>
+    <t>111-307SUBAAD</t>
+  </si>
+  <si>
+    <t>113-517SUBAAD</t>
+  </si>
+  <si>
+    <t>111-350SUBAAD</t>
+  </si>
+  <si>
+    <t>289-351SUBAAD</t>
+  </si>
+  <si>
+    <t>111-360SUBAAD</t>
+  </si>
+  <si>
+    <t>111-366SUBAAD</t>
+  </si>
+  <si>
+    <t>111-370SUBAAD</t>
+  </si>
+  <si>
+    <t>111-301SUBAAD</t>
+  </si>
+  <si>
+    <t>111-308SUBAAD</t>
+  </si>
+  <si>
+    <t>115-845SUBAAD</t>
+  </si>
+  <si>
+    <t>340-170SUBAAD</t>
+  </si>
+  <si>
+    <t>340-175SUBAAD</t>
+  </si>
+  <si>
+    <t>323-723SUBAAD</t>
+  </si>
+  <si>
+    <t>323-720SUBAAD</t>
+  </si>
+  <si>
+    <t>111-302SUBAAD</t>
+  </si>
+  <si>
+    <t>CXO-CXOSUBAAD</t>
+  </si>
+  <si>
+    <t>IHS-IHSSUBAAD</t>
+  </si>
+  <si>
+    <t>113-540SUBAAD</t>
+  </si>
+  <si>
+    <t>111-595SUBAAD</t>
+  </si>
+  <si>
+    <t>213-595SUBAAD</t>
+  </si>
+  <si>
+    <t>909-950SUBAAD</t>
+  </si>
+  <si>
+    <t>900-965SUBAAD</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>950</t>
+  </si>
+  <si>
+    <t>905</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>SACADV</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>CXO</t>
+  </si>
+  <si>
+    <t>IHS</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>351</t>
+  </si>
+  <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>845</t>
+  </si>
+  <si>
+    <t>723</t>
+  </si>
+  <si>
+    <t>720</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>595</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="000000"/>
-    <numFmt numFmtId="176" formatCode="000\-000000000000000"/>
+    <numFmt numFmtId="164" formatCode="000000"/>
+    <numFmt numFmtId="165" formatCode="000\-000000000000000"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -385,13 +773,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -412,11 +801,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma 2 3" xfId="4" xr:uid="{2752E66A-4F67-40AA-B7EF-E254D1B4A439}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{50188739-D34B-4882-A35E-7E5CAB42D389}"/>
     <cellStyle name="Normal 2 2" xfId="3" xr:uid="{3BF04DFD-C6E8-423D-BE24-7A52253C3C26}"/>
@@ -430,18 +822,18 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i/>
         <color rgb="FF00B050"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -773,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48D137C4-8712-4B12-ABE6-1DA52A339D86}">
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V106"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.625" customWidth="1"/>
@@ -1017,7 +1409,7 @@
         <v>26</v>
       </c>
       <c r="D13">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F13" t="s">
         <v>38</v>
@@ -1045,11 +1437,11 @@
         <v>32</v>
       </c>
       <c r="N13">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="O13" t="str">
         <f t="shared" ref="O13" si="0">_xlfn.CONCAT(D13,"_",N13)</f>
-        <v>111_170</v>
+        <v>113_100</v>
       </c>
       <c r="P13" t="s">
         <v>31</v>
@@ -1071,7 +1463,7 @@
       </c>
       <c r="V13">
         <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(B13,C13,D13,E13,F13,G13,H13,I13,J13,K13,L13,M13,N13,O13,P13,Q13,R13,S13,T13,U13)</f>
-        <v>5525947.3300000001</v>
+        <v>171948.07</v>
       </c>
     </row>
     <row r="24" spans="2:2">
@@ -1079,18 +1471,894 @@
         <v>84</v>
       </c>
     </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="str">
+        <f>LEFT(A38,3)</f>
+        <v>113</v>
+      </c>
+      <c r="N38" t="str">
+        <f>MID(A38,5,3)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
+      <c r="A39" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" t="str">
+        <f t="shared" ref="D39:D102" si="1">LEFT(A39,3)</f>
+        <v>113</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" ref="N39:N102" si="2">MID(A39,5,3)</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
+      <c r="A40" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N42" t="str">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N43" t="str">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" t="s">
+        <v>94</v>
+      </c>
+      <c r="D44" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N44" t="str">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="2"/>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="2"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N48" t="str">
+        <f t="shared" si="2"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N49" t="str">
+        <f t="shared" si="2"/>
+        <v>443</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D50" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="shared" si="2"/>
+        <v>444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>101</v>
+      </c>
+      <c r="D51" t="str">
+        <f t="shared" si="1"/>
+        <v>291</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="2"/>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" t="str">
+        <f t="shared" si="1"/>
+        <v>213</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="shared" si="2"/>
+        <v>445</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>103</v>
+      </c>
+      <c r="D53" t="str">
+        <f t="shared" si="1"/>
+        <v>213</v>
+      </c>
+      <c r="N53" t="str">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="D54" t="str">
+        <f t="shared" si="1"/>
+        <v>213</v>
+      </c>
+      <c r="N54" t="str">
+        <f t="shared" si="2"/>
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" t="s">
+        <v>105</v>
+      </c>
+      <c r="D55" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N55" t="str">
+        <f t="shared" si="2"/>
+        <v>449</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="D56" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N56" t="str">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" t="str">
+        <f t="shared" si="1"/>
+        <v>213</v>
+      </c>
+      <c r="N57" t="str">
+        <f t="shared" si="2"/>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N58" t="str">
+        <f t="shared" si="2"/>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N59" t="str">
+        <f t="shared" si="2"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N60" t="str">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>111</v>
+      </c>
+      <c r="D61" t="str">
+        <f t="shared" si="1"/>
+        <v>900</v>
+      </c>
+      <c r="N61" t="str">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="str">
+        <f t="shared" si="1"/>
+        <v>905</v>
+      </c>
+      <c r="N62" t="str">
+        <f t="shared" si="2"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" t="s">
+        <v>85</v>
+      </c>
+      <c r="D63" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N63" t="str">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="D64" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" t="s">
+        <v>113</v>
+      </c>
+      <c r="D65" t="str">
+        <f t="shared" si="1"/>
+        <v>186</v>
+      </c>
+      <c r="N65" t="str">
+        <f t="shared" si="2"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N66" t="str">
+        <f t="shared" si="2"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" t="s">
+        <v>115</v>
+      </c>
+      <c r="D67" t="str">
+        <f t="shared" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="N67" t="str">
+        <f t="shared" si="2"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" t="s">
+        <v>116</v>
+      </c>
+      <c r="D68" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N68" t="str">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N69" t="str">
+        <f t="shared" si="2"/>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
+      <c r="A70" t="s">
+        <v>118</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N70" t="str">
+        <f t="shared" si="2"/>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" t="s">
+        <v>119</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N71" t="str">
+        <f t="shared" si="2"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N72" t="str">
+        <f t="shared" si="2"/>
+        <v>525</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
+      <c r="A73" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="1"/>
+        <v>IT-</v>
+      </c>
+      <c r="N73" t="str">
+        <f t="shared" si="2"/>
+        <v xml:space="preserve">13 </v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N74" t="str">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
+      <c r="D75" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
+      <c r="A76" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N76" t="str">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
+      <c r="A77" t="s">
+        <v>123</v>
+      </c>
+      <c r="D77" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N77" t="str">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
+      <c r="A78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D78" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N78" t="str">
+        <f t="shared" si="2"/>
+        <v>513</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
+      <c r="A79" t="s">
+        <v>125</v>
+      </c>
+      <c r="D79" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N79" t="str">
+        <f t="shared" si="2"/>
+        <v>519</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
+      <c r="A80" t="s">
+        <v>126</v>
+      </c>
+      <c r="D80" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N80" t="str">
+        <f t="shared" si="2"/>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D81" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N81" t="str">
+        <f t="shared" si="2"/>
+        <v>510</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" t="s">
+        <v>128</v>
+      </c>
+      <c r="D82" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N82" t="str">
+        <f t="shared" si="2"/>
+        <v>518</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" t="s">
+        <v>129</v>
+      </c>
+      <c r="D83" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N83" t="str">
+        <f t="shared" si="2"/>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" t="s">
+        <v>130</v>
+      </c>
+      <c r="D84" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N84" t="str">
+        <f t="shared" si="2"/>
+        <v>517</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" t="s">
+        <v>131</v>
+      </c>
+      <c r="D85" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N85" t="str">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" t="s">
+        <v>132</v>
+      </c>
+      <c r="D86" t="str">
+        <f t="shared" si="1"/>
+        <v>289</v>
+      </c>
+      <c r="N86" t="str">
+        <f t="shared" si="2"/>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" t="s">
+        <v>133</v>
+      </c>
+      <c r="D87" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N87" t="str">
+        <f t="shared" si="2"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" t="s">
+        <v>134</v>
+      </c>
+      <c r="D88" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N88" t="str">
+        <f t="shared" si="2"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" t="s">
+        <v>135</v>
+      </c>
+      <c r="D89" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N89" t="str">
+        <f t="shared" si="2"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" t="s">
+        <v>136</v>
+      </c>
+      <c r="D90" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N90" t="str">
+        <f t="shared" si="2"/>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" t="s">
+        <v>137</v>
+      </c>
+      <c r="D91" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N91" t="str">
+        <f t="shared" si="2"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" t="s">
+        <v>138</v>
+      </c>
+      <c r="D92" t="str">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="N92" t="str">
+        <f t="shared" si="2"/>
+        <v>845</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
+      <c r="A93" t="s">
+        <v>139</v>
+      </c>
+      <c r="D93" t="str">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="N93" t="str">
+        <f t="shared" si="2"/>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
+      <c r="A94" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" t="str">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="N94" t="str">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
+      <c r="A95" t="s">
+        <v>141</v>
+      </c>
+      <c r="D95" t="str">
+        <f t="shared" si="1"/>
+        <v>323</v>
+      </c>
+      <c r="N95" t="str">
+        <f t="shared" si="2"/>
+        <v>723</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
+      <c r="A96" t="s">
+        <v>142</v>
+      </c>
+      <c r="D96" t="str">
+        <f t="shared" si="1"/>
+        <v>323</v>
+      </c>
+      <c r="N96" t="str">
+        <f t="shared" si="2"/>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
+      <c r="A97" t="s">
+        <v>143</v>
+      </c>
+      <c r="D97" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N97" t="str">
+        <f t="shared" si="2"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
+      <c r="A98" t="s">
+        <v>144</v>
+      </c>
+      <c r="D98" t="str">
+        <f t="shared" si="1"/>
+        <v>CXO</v>
+      </c>
+      <c r="N98" t="str">
+        <f t="shared" si="2"/>
+        <v>CXO</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
+      <c r="A99" t="s">
+        <v>145</v>
+      </c>
+      <c r="D99" t="str">
+        <f t="shared" si="1"/>
+        <v>IHS</v>
+      </c>
+      <c r="N99" t="str">
+        <f t="shared" si="2"/>
+        <v>IHS</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
+      <c r="A100" t="s">
+        <v>146</v>
+      </c>
+      <c r="D100" t="str">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="N100" t="str">
+        <f t="shared" si="2"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
+      <c r="A101" t="s">
+        <v>147</v>
+      </c>
+      <c r="D101" t="str">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="N101" t="str">
+        <f t="shared" si="2"/>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
+      <c r="A102" t="s">
+        <v>148</v>
+      </c>
+      <c r="D102" t="str">
+        <f t="shared" si="1"/>
+        <v>213</v>
+      </c>
+      <c r="N102" t="str">
+        <f t="shared" si="2"/>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
+      <c r="D103" t="str">
+        <f t="shared" ref="D103:D105" si="3">LEFT(A103,3)</f>
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <f t="shared" ref="N103:N106" si="4">MID(A103,5,3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
+      <c r="A104" t="s">
+        <v>149</v>
+      </c>
+      <c r="D104" t="str">
+        <f t="shared" si="3"/>
+        <v>909</v>
+      </c>
+      <c r="N104" t="str">
+        <f t="shared" si="4"/>
+        <v>950</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
+      <c r="A105" t="s">
+        <v>150</v>
+      </c>
+      <c r="D105" t="str">
+        <f t="shared" si="3"/>
+        <v>900</v>
+      </c>
+      <c r="N105" t="str">
+        <f t="shared" si="4"/>
+        <v>965</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
+      <c r="A106" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C4:U4">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="FALSE">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>ISNUMBER(SEARCH(".xl", _xlfn.FORMULATEXT(C4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="FALSE">
       <formula>NOT(ISERROR(SEARCH("FALSE",C4)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:U4">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>ISNUMBER(SEARCH(".xl", _xlfn.FORMULATEXT(C4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4:U4">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",C4)))</formula>
     </cfRule>
@@ -1328,7 +2596,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FB1A4C-127C-4EF9-9801-A1E1DDD532CD}">
-  <dimension ref="A1:U237"/>
+  <dimension ref="A1:U299"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
@@ -16741,6 +18009,4034 @@
         <v>0</v>
       </c>
     </row>
+    <row r="238" spans="1:21">
+      <c r="A238" t="b">
+        <v>1</v>
+      </c>
+      <c r="B238" t="s">
+        <v>26</v>
+      </c>
+      <c r="C238" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E238" t="s">
+        <v>38</v>
+      </c>
+      <c r="F238" t="s">
+        <v>27</v>
+      </c>
+      <c r="G238" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H238" t="s">
+        <v>29</v>
+      </c>
+      <c r="I238" t="s">
+        <v>83</v>
+      </c>
+      <c r="J238" t="s">
+        <v>41</v>
+      </c>
+      <c r="K238" t="s">
+        <v>31</v>
+      </c>
+      <c r="L238" t="s">
+        <v>32</v>
+      </c>
+      <c r="M238" s="13">
+        <v>100</v>
+      </c>
+      <c r="N238" t="str">
+        <f t="shared" ref="N238:N262" si="4">_xlfn.CONCAT(C238,"_",M238)</f>
+        <v>113_100</v>
+      </c>
+      <c r="O238" t="s">
+        <v>31</v>
+      </c>
+      <c r="P238" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>31</v>
+      </c>
+      <c r="R238" t="s">
+        <v>31</v>
+      </c>
+      <c r="S238" t="s">
+        <v>31</v>
+      </c>
+      <c r="T238" t="s">
+        <v>31</v>
+      </c>
+      <c r="U238">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A238,B238,C238,D238,E238,F238,G238,H238,I238,J238,K238,L238,M238,N238,O238,P238,Q238,R238,S238,T238)</f>
+        <v>171948.07</v>
+      </c>
+    </row>
+    <row r="239" spans="1:21">
+      <c r="A239" t="b">
+        <v>1</v>
+      </c>
+      <c r="B239" t="s">
+        <v>26</v>
+      </c>
+      <c r="C239" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E239" t="s">
+        <v>38</v>
+      </c>
+      <c r="F239" t="s">
+        <v>27</v>
+      </c>
+      <c r="G239" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H239" t="s">
+        <v>29</v>
+      </c>
+      <c r="I239" t="s">
+        <v>83</v>
+      </c>
+      <c r="J239" t="s">
+        <v>41</v>
+      </c>
+      <c r="K239" t="s">
+        <v>31</v>
+      </c>
+      <c r="L239" t="s">
+        <v>32</v>
+      </c>
+      <c r="M239" t="s">
+        <v>153</v>
+      </c>
+      <c r="N239" t="str">
+        <f t="shared" si="4"/>
+        <v>113_101</v>
+      </c>
+      <c r="O239" t="s">
+        <v>31</v>
+      </c>
+      <c r="P239" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>31</v>
+      </c>
+      <c r="R239" t="s">
+        <v>31</v>
+      </c>
+      <c r="S239" t="s">
+        <v>31</v>
+      </c>
+      <c r="T239" t="s">
+        <v>31</v>
+      </c>
+      <c r="U239">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A239,B239,C239,D239,E239,F239,G239,H239,I239,J239,K239,L239,M239,N239,O239,P239,Q239,R239,S239,T239)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:21">
+      <c r="A240" t="b">
+        <v>1</v>
+      </c>
+      <c r="B240" t="s">
+        <v>26</v>
+      </c>
+      <c r="C240" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E240" t="s">
+        <v>38</v>
+      </c>
+      <c r="F240" t="s">
+        <v>27</v>
+      </c>
+      <c r="G240" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H240" t="s">
+        <v>29</v>
+      </c>
+      <c r="I240" t="s">
+        <v>83</v>
+      </c>
+      <c r="J240" t="s">
+        <v>41</v>
+      </c>
+      <c r="K240" t="s">
+        <v>31</v>
+      </c>
+      <c r="L240" t="s">
+        <v>32</v>
+      </c>
+      <c r="M240" t="s">
+        <v>154</v>
+      </c>
+      <c r="N240" t="str">
+        <f t="shared" si="4"/>
+        <v>113_102</v>
+      </c>
+      <c r="O240" t="s">
+        <v>31</v>
+      </c>
+      <c r="P240" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>31</v>
+      </c>
+      <c r="R240" t="s">
+        <v>31</v>
+      </c>
+      <c r="S240" t="s">
+        <v>31</v>
+      </c>
+      <c r="T240" t="s">
+        <v>31</v>
+      </c>
+      <c r="U240">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A240,B240,C240,D240,E240,F240,G240,H240,I240,J240,K240,L240,M240,N240,O240,P240,Q240,R240,S240,T240)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:21">
+      <c r="A241" t="b">
+        <v>1</v>
+      </c>
+      <c r="B241" t="s">
+        <v>26</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E241" t="s">
+        <v>38</v>
+      </c>
+      <c r="F241" t="s">
+        <v>27</v>
+      </c>
+      <c r="G241" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H241" t="s">
+        <v>29</v>
+      </c>
+      <c r="I241" t="s">
+        <v>83</v>
+      </c>
+      <c r="J241" t="s">
+        <v>41</v>
+      </c>
+      <c r="K241" t="s">
+        <v>31</v>
+      </c>
+      <c r="L241" t="s">
+        <v>32</v>
+      </c>
+      <c r="M241" t="s">
+        <v>155</v>
+      </c>
+      <c r="N241" t="str">
+        <f t="shared" si="4"/>
+        <v>113_103</v>
+      </c>
+      <c r="O241" t="s">
+        <v>31</v>
+      </c>
+      <c r="P241" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>31</v>
+      </c>
+      <c r="R241" t="s">
+        <v>31</v>
+      </c>
+      <c r="S241" t="s">
+        <v>31</v>
+      </c>
+      <c r="T241" t="s">
+        <v>31</v>
+      </c>
+      <c r="U241">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A241,B241,C241,D241,E241,F241,G241,H241,I241,J241,K241,L241,M241,N241,O241,P241,Q241,R241,S241,T241)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:21">
+      <c r="A242" t="b">
+        <v>1</v>
+      </c>
+      <c r="B242" t="s">
+        <v>26</v>
+      </c>
+      <c r="C242" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E242" t="s">
+        <v>38</v>
+      </c>
+      <c r="F242" t="s">
+        <v>27</v>
+      </c>
+      <c r="G242" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H242" t="s">
+        <v>29</v>
+      </c>
+      <c r="I242" t="s">
+        <v>83</v>
+      </c>
+      <c r="J242" t="s">
+        <v>41</v>
+      </c>
+      <c r="K242" t="s">
+        <v>31</v>
+      </c>
+      <c r="L242" t="s">
+        <v>32</v>
+      </c>
+      <c r="M242" t="s">
+        <v>156</v>
+      </c>
+      <c r="N242" t="str">
+        <f t="shared" si="4"/>
+        <v>113_120</v>
+      </c>
+      <c r="O242" t="s">
+        <v>31</v>
+      </c>
+      <c r="P242" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>31</v>
+      </c>
+      <c r="R242" t="s">
+        <v>31</v>
+      </c>
+      <c r="S242" t="s">
+        <v>31</v>
+      </c>
+      <c r="T242" t="s">
+        <v>31</v>
+      </c>
+      <c r="U242">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A242,B242,C242,D242,E242,F242,G242,H242,I242,J242,K242,L242,M242,N242,O242,P242,Q242,R242,S242,T242)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:21">
+      <c r="A243" t="b">
+        <v>1</v>
+      </c>
+      <c r="B243" t="s">
+        <v>26</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E243" t="s">
+        <v>38</v>
+      </c>
+      <c r="F243" t="s">
+        <v>27</v>
+      </c>
+      <c r="G243" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H243" t="s">
+        <v>29</v>
+      </c>
+      <c r="I243" t="s">
+        <v>83</v>
+      </c>
+      <c r="J243" t="s">
+        <v>41</v>
+      </c>
+      <c r="K243" t="s">
+        <v>31</v>
+      </c>
+      <c r="L243" t="s">
+        <v>32</v>
+      </c>
+      <c r="M243" t="s">
+        <v>157</v>
+      </c>
+      <c r="N243" t="str">
+        <f t="shared" si="4"/>
+        <v>113_125</v>
+      </c>
+      <c r="O243" t="s">
+        <v>31</v>
+      </c>
+      <c r="P243" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>31</v>
+      </c>
+      <c r="R243" t="s">
+        <v>31</v>
+      </c>
+      <c r="S243" t="s">
+        <v>31</v>
+      </c>
+      <c r="T243" t="s">
+        <v>31</v>
+      </c>
+      <c r="U243">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A243,B243,C243,D243,E243,F243,G243,H243,I243,J243,K243,L243,M243,N243,O243,P243,Q243,R243,S243,T243)</f>
+        <v>1409.57</v>
+      </c>
+    </row>
+    <row r="244" spans="1:21">
+      <c r="A244" t="b">
+        <v>1</v>
+      </c>
+      <c r="B244" t="s">
+        <v>26</v>
+      </c>
+      <c r="C244" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E244" t="s">
+        <v>38</v>
+      </c>
+      <c r="F244" t="s">
+        <v>27</v>
+      </c>
+      <c r="G244" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H244" t="s">
+        <v>29</v>
+      </c>
+      <c r="I244" t="s">
+        <v>83</v>
+      </c>
+      <c r="J244" t="s">
+        <v>41</v>
+      </c>
+      <c r="K244" t="s">
+        <v>31</v>
+      </c>
+      <c r="L244" t="s">
+        <v>32</v>
+      </c>
+      <c r="M244" t="s">
+        <v>158</v>
+      </c>
+      <c r="N244" t="str">
+        <f t="shared" si="4"/>
+        <v>113_130</v>
+      </c>
+      <c r="O244" t="s">
+        <v>31</v>
+      </c>
+      <c r="P244" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>31</v>
+      </c>
+      <c r="R244" t="s">
+        <v>31</v>
+      </c>
+      <c r="S244" t="s">
+        <v>31</v>
+      </c>
+      <c r="T244" t="s">
+        <v>31</v>
+      </c>
+      <c r="U244">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A244,B244,C244,D244,E244,F244,G244,H244,I244,J244,K244,L244,M244,N244,O244,P244,Q244,R244,S244,T244)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:21">
+      <c r="A245" t="b">
+        <v>1</v>
+      </c>
+      <c r="B245" t="s">
+        <v>26</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E245" t="s">
+        <v>38</v>
+      </c>
+      <c r="F245" t="s">
+        <v>27</v>
+      </c>
+      <c r="G245" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H245" t="s">
+        <v>29</v>
+      </c>
+      <c r="I245" t="s">
+        <v>83</v>
+      </c>
+      <c r="J245" t="s">
+        <v>41</v>
+      </c>
+      <c r="K245" t="s">
+        <v>31</v>
+      </c>
+      <c r="L245" t="s">
+        <v>32</v>
+      </c>
+      <c r="M245" t="s">
+        <v>159</v>
+      </c>
+      <c r="N245" t="str">
+        <f t="shared" si="4"/>
+        <v>113_131</v>
+      </c>
+      <c r="O245" t="s">
+        <v>31</v>
+      </c>
+      <c r="P245" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>31</v>
+      </c>
+      <c r="R245" t="s">
+        <v>31</v>
+      </c>
+      <c r="S245" t="s">
+        <v>31</v>
+      </c>
+      <c r="T245" t="s">
+        <v>31</v>
+      </c>
+      <c r="U245">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A245,B245,C245,D245,E245,F245,G245,H245,I245,J245,K245,L245,M245,N245,O245,P245,Q245,R245,S245,T245)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:21">
+      <c r="A246" t="b">
+        <v>1</v>
+      </c>
+      <c r="B246" t="s">
+        <v>26</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E246" t="s">
+        <v>38</v>
+      </c>
+      <c r="F246" t="s">
+        <v>27</v>
+      </c>
+      <c r="G246" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H246" t="s">
+        <v>29</v>
+      </c>
+      <c r="I246" t="s">
+        <v>83</v>
+      </c>
+      <c r="J246" t="s">
+        <v>41</v>
+      </c>
+      <c r="K246" t="s">
+        <v>31</v>
+      </c>
+      <c r="L246" t="s">
+        <v>32</v>
+      </c>
+      <c r="M246" t="s">
+        <v>160</v>
+      </c>
+      <c r="N246" t="str">
+        <f t="shared" si="4"/>
+        <v>113_135</v>
+      </c>
+      <c r="O246" t="s">
+        <v>31</v>
+      </c>
+      <c r="P246" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>31</v>
+      </c>
+      <c r="R246" t="s">
+        <v>31</v>
+      </c>
+      <c r="S246" t="s">
+        <v>31</v>
+      </c>
+      <c r="T246" t="s">
+        <v>31</v>
+      </c>
+      <c r="U246">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A246,B246,C246,D246,E246,F246,G246,H246,I246,J246,K246,L246,M246,N246,O246,P246,Q246,R246,S246,T246)</f>
+        <v>-2244.38</v>
+      </c>
+    </row>
+    <row r="247" spans="1:21">
+      <c r="A247" t="b">
+        <v>1</v>
+      </c>
+      <c r="B247" t="s">
+        <v>26</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E247" t="s">
+        <v>38</v>
+      </c>
+      <c r="F247" t="s">
+        <v>27</v>
+      </c>
+      <c r="G247" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H247" t="s">
+        <v>29</v>
+      </c>
+      <c r="I247" t="s">
+        <v>83</v>
+      </c>
+      <c r="J247" t="s">
+        <v>41</v>
+      </c>
+      <c r="K247" t="s">
+        <v>31</v>
+      </c>
+      <c r="L247" t="s">
+        <v>32</v>
+      </c>
+      <c r="M247" t="s">
+        <v>161</v>
+      </c>
+      <c r="N247" t="str">
+        <f t="shared" si="4"/>
+        <v>113_115</v>
+      </c>
+      <c r="O247" t="s">
+        <v>31</v>
+      </c>
+      <c r="P247" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>31</v>
+      </c>
+      <c r="R247" t="s">
+        <v>31</v>
+      </c>
+      <c r="S247" t="s">
+        <v>31</v>
+      </c>
+      <c r="T247" t="s">
+        <v>31</v>
+      </c>
+      <c r="U247">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A247,B247,C247,D247,E247,F247,G247,H247,I247,J247,K247,L247,M247,N247,O247,P247,Q247,R247,S247,T247)</f>
+        <v>125925.68</v>
+      </c>
+    </row>
+    <row r="248" spans="1:21">
+      <c r="A248" t="b">
+        <v>1</v>
+      </c>
+      <c r="B248" t="s">
+        <v>26</v>
+      </c>
+      <c r="C248" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E248" t="s">
+        <v>38</v>
+      </c>
+      <c r="F248" t="s">
+        <v>27</v>
+      </c>
+      <c r="G248" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H248" t="s">
+        <v>29</v>
+      </c>
+      <c r="I248" t="s">
+        <v>83</v>
+      </c>
+      <c r="J248" t="s">
+        <v>41</v>
+      </c>
+      <c r="K248" t="s">
+        <v>31</v>
+      </c>
+      <c r="L248" t="s">
+        <v>32</v>
+      </c>
+      <c r="M248" t="s">
+        <v>162</v>
+      </c>
+      <c r="N248" t="str">
+        <f t="shared" si="4"/>
+        <v>113_132</v>
+      </c>
+      <c r="O248" t="s">
+        <v>31</v>
+      </c>
+      <c r="P248" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>31</v>
+      </c>
+      <c r="R248" t="s">
+        <v>31</v>
+      </c>
+      <c r="S248" t="s">
+        <v>31</v>
+      </c>
+      <c r="T248" t="s">
+        <v>31</v>
+      </c>
+      <c r="U248">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A248,B248,C248,D248,E248,F248,G248,H248,I248,J248,K248,L248,M248,N248,O248,P248,Q248,R248,S248,T248)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:21">
+      <c r="A249" t="b">
+        <v>1</v>
+      </c>
+      <c r="B249" t="s">
+        <v>26</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E249" t="s">
+        <v>38</v>
+      </c>
+      <c r="F249" t="s">
+        <v>27</v>
+      </c>
+      <c r="G249" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H249" t="s">
+        <v>29</v>
+      </c>
+      <c r="I249" t="s">
+        <v>83</v>
+      </c>
+      <c r="J249" t="s">
+        <v>41</v>
+      </c>
+      <c r="K249" t="s">
+        <v>31</v>
+      </c>
+      <c r="L249" t="s">
+        <v>32</v>
+      </c>
+      <c r="M249" t="s">
+        <v>164</v>
+      </c>
+      <c r="N249" t="str">
+        <f t="shared" si="4"/>
+        <v>111_443</v>
+      </c>
+      <c r="O249" t="s">
+        <v>31</v>
+      </c>
+      <c r="P249" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>31</v>
+      </c>
+      <c r="R249" t="s">
+        <v>31</v>
+      </c>
+      <c r="S249" t="s">
+        <v>31</v>
+      </c>
+      <c r="T249" t="s">
+        <v>31</v>
+      </c>
+      <c r="U249">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A249,B249,C249,D249,E249,F249,G249,H249,I249,J249,K249,L249,M249,N249,O249,P249,Q249,R249,S249,T249)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:21">
+      <c r="A250" t="b">
+        <v>1</v>
+      </c>
+      <c r="B250" t="s">
+        <v>26</v>
+      </c>
+      <c r="C250" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E250" t="s">
+        <v>38</v>
+      </c>
+      <c r="F250" t="s">
+        <v>27</v>
+      </c>
+      <c r="G250" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H250" t="s">
+        <v>29</v>
+      </c>
+      <c r="I250" t="s">
+        <v>83</v>
+      </c>
+      <c r="J250" t="s">
+        <v>41</v>
+      </c>
+      <c r="K250" t="s">
+        <v>31</v>
+      </c>
+      <c r="L250" t="s">
+        <v>32</v>
+      </c>
+      <c r="M250" t="s">
+        <v>165</v>
+      </c>
+      <c r="N250" t="str">
+        <f t="shared" si="4"/>
+        <v>111_444</v>
+      </c>
+      <c r="O250" t="s">
+        <v>31</v>
+      </c>
+      <c r="P250" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>31</v>
+      </c>
+      <c r="R250" t="s">
+        <v>31</v>
+      </c>
+      <c r="S250" t="s">
+        <v>31</v>
+      </c>
+      <c r="T250" t="s">
+        <v>31</v>
+      </c>
+      <c r="U250">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A250,B250,C250,D250,E250,F250,G250,H250,I250,J250,K250,L250,M250,N250,O250,P250,Q250,R250,S250,T250)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:21">
+      <c r="A251" t="b">
+        <v>1</v>
+      </c>
+      <c r="B251" t="s">
+        <v>26</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E251" t="s">
+        <v>38</v>
+      </c>
+      <c r="F251" t="s">
+        <v>27</v>
+      </c>
+      <c r="G251" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H251" t="s">
+        <v>29</v>
+      </c>
+      <c r="I251" t="s">
+        <v>83</v>
+      </c>
+      <c r="J251" t="s">
+        <v>41</v>
+      </c>
+      <c r="K251" t="s">
+        <v>31</v>
+      </c>
+      <c r="L251" t="s">
+        <v>32</v>
+      </c>
+      <c r="M251" t="s">
+        <v>167</v>
+      </c>
+      <c r="N251" t="str">
+        <f t="shared" si="4"/>
+        <v>291_307</v>
+      </c>
+      <c r="O251" t="s">
+        <v>31</v>
+      </c>
+      <c r="P251" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>31</v>
+      </c>
+      <c r="R251" t="s">
+        <v>31</v>
+      </c>
+      <c r="S251" t="s">
+        <v>31</v>
+      </c>
+      <c r="T251" t="s">
+        <v>31</v>
+      </c>
+      <c r="U251">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A251,B251,C251,D251,E251,F251,G251,H251,I251,J251,K251,L251,M251,N251,O251,P251,Q251,R251,S251,T251)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:21">
+      <c r="A252" t="b">
+        <v>1</v>
+      </c>
+      <c r="B252" t="s">
+        <v>26</v>
+      </c>
+      <c r="C252" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E252" t="s">
+        <v>38</v>
+      </c>
+      <c r="F252" t="s">
+        <v>27</v>
+      </c>
+      <c r="G252" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H252" t="s">
+        <v>29</v>
+      </c>
+      <c r="I252" t="s">
+        <v>83</v>
+      </c>
+      <c r="J252" t="s">
+        <v>41</v>
+      </c>
+      <c r="K252" t="s">
+        <v>31</v>
+      </c>
+      <c r="L252" t="s">
+        <v>32</v>
+      </c>
+      <c r="M252" t="s">
+        <v>169</v>
+      </c>
+      <c r="N252" t="str">
+        <f t="shared" si="4"/>
+        <v>213_445</v>
+      </c>
+      <c r="O252" t="s">
+        <v>31</v>
+      </c>
+      <c r="P252" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>31</v>
+      </c>
+      <c r="R252" t="s">
+        <v>31</v>
+      </c>
+      <c r="S252" t="s">
+        <v>31</v>
+      </c>
+      <c r="T252" t="s">
+        <v>31</v>
+      </c>
+      <c r="U252">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A252,B252,C252,D252,E252,F252,G252,H252,I252,J252,K252,L252,M252,N252,O252,P252,Q252,R252,S252,T252)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:21">
+      <c r="A253" t="b">
+        <v>1</v>
+      </c>
+      <c r="B253" t="s">
+        <v>26</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E253" t="s">
+        <v>38</v>
+      </c>
+      <c r="F253" t="s">
+        <v>27</v>
+      </c>
+      <c r="G253" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H253" t="s">
+        <v>29</v>
+      </c>
+      <c r="I253" t="s">
+        <v>83</v>
+      </c>
+      <c r="J253" t="s">
+        <v>41</v>
+      </c>
+      <c r="K253" t="s">
+        <v>31</v>
+      </c>
+      <c r="L253" t="s">
+        <v>32</v>
+      </c>
+      <c r="M253" t="s">
+        <v>152</v>
+      </c>
+      <c r="N253" t="str">
+        <f t="shared" si="4"/>
+        <v>213_100</v>
+      </c>
+      <c r="O253" t="s">
+        <v>31</v>
+      </c>
+      <c r="P253" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>31</v>
+      </c>
+      <c r="R253" t="s">
+        <v>31</v>
+      </c>
+      <c r="S253" t="s">
+        <v>31</v>
+      </c>
+      <c r="T253" t="s">
+        <v>31</v>
+      </c>
+      <c r="U253">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A253,B253,C253,D253,E253,F253,G253,H253,I253,J253,K253,L253,M253,N253,O253,P253,Q253,R253,S253,T253)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:21">
+      <c r="A254" t="b">
+        <v>1</v>
+      </c>
+      <c r="B254" t="s">
+        <v>26</v>
+      </c>
+      <c r="C254" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E254" t="s">
+        <v>38</v>
+      </c>
+      <c r="F254" t="s">
+        <v>27</v>
+      </c>
+      <c r="G254" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H254" t="s">
+        <v>29</v>
+      </c>
+      <c r="I254" t="s">
+        <v>83</v>
+      </c>
+      <c r="J254" t="s">
+        <v>41</v>
+      </c>
+      <c r="K254" t="s">
+        <v>31</v>
+      </c>
+      <c r="L254" t="s">
+        <v>32</v>
+      </c>
+      <c r="M254" t="s">
+        <v>156</v>
+      </c>
+      <c r="N254" t="str">
+        <f t="shared" si="4"/>
+        <v>213_120</v>
+      </c>
+      <c r="O254" t="s">
+        <v>31</v>
+      </c>
+      <c r="P254" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>31</v>
+      </c>
+      <c r="R254" t="s">
+        <v>31</v>
+      </c>
+      <c r="S254" t="s">
+        <v>31</v>
+      </c>
+      <c r="T254" t="s">
+        <v>31</v>
+      </c>
+      <c r="U254">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A254,B254,C254,D254,E254,F254,G254,H254,I254,J254,K254,L254,M254,N254,O254,P254,Q254,R254,S254,T254)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:21">
+      <c r="A255" t="b">
+        <v>1</v>
+      </c>
+      <c r="B255" t="s">
+        <v>26</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E255" t="s">
+        <v>38</v>
+      </c>
+      <c r="F255" t="s">
+        <v>27</v>
+      </c>
+      <c r="G255" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H255" t="s">
+        <v>29</v>
+      </c>
+      <c r="I255" t="s">
+        <v>83</v>
+      </c>
+      <c r="J255" t="s">
+        <v>41</v>
+      </c>
+      <c r="K255" t="s">
+        <v>31</v>
+      </c>
+      <c r="L255" t="s">
+        <v>32</v>
+      </c>
+      <c r="M255" t="s">
+        <v>170</v>
+      </c>
+      <c r="N255" t="str">
+        <f t="shared" si="4"/>
+        <v>111_449</v>
+      </c>
+      <c r="O255" t="s">
+        <v>31</v>
+      </c>
+      <c r="P255" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>31</v>
+      </c>
+      <c r="R255" t="s">
+        <v>31</v>
+      </c>
+      <c r="S255" t="s">
+        <v>31</v>
+      </c>
+      <c r="T255" t="s">
+        <v>31</v>
+      </c>
+      <c r="U255">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A255,B255,C255,D255,E255,F255,G255,H255,I255,J255,K255,L255,M255,N255,O255,P255,Q255,R255,S255,T255)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:21">
+      <c r="A256" t="b">
+        <v>1</v>
+      </c>
+      <c r="B256" t="s">
+        <v>26</v>
+      </c>
+      <c r="C256" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E256" t="s">
+        <v>38</v>
+      </c>
+      <c r="F256" t="s">
+        <v>27</v>
+      </c>
+      <c r="G256" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H256" t="s">
+        <v>29</v>
+      </c>
+      <c r="I256" t="s">
+        <v>83</v>
+      </c>
+      <c r="J256" t="s">
+        <v>41</v>
+      </c>
+      <c r="K256" t="s">
+        <v>31</v>
+      </c>
+      <c r="L256" t="s">
+        <v>32</v>
+      </c>
+      <c r="M256" t="s">
+        <v>158</v>
+      </c>
+      <c r="N256" t="str">
+        <f t="shared" si="4"/>
+        <v>111_130</v>
+      </c>
+      <c r="O256" t="s">
+        <v>31</v>
+      </c>
+      <c r="P256" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>31</v>
+      </c>
+      <c r="R256" t="s">
+        <v>31</v>
+      </c>
+      <c r="S256" t="s">
+        <v>31</v>
+      </c>
+      <c r="T256" t="s">
+        <v>31</v>
+      </c>
+      <c r="U256">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A256,B256,C256,D256,E256,F256,G256,H256,I256,J256,K256,L256,M256,N256,O256,P256,Q256,R256,S256,T256)</f>
+        <v>168531.15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:21">
+      <c r="A257" t="b">
+        <v>1</v>
+      </c>
+      <c r="B257" t="s">
+        <v>26</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E257" t="s">
+        <v>38</v>
+      </c>
+      <c r="F257" t="s">
+        <v>27</v>
+      </c>
+      <c r="G257" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H257" t="s">
+        <v>29</v>
+      </c>
+      <c r="I257" t="s">
+        <v>83</v>
+      </c>
+      <c r="J257" t="s">
+        <v>41</v>
+      </c>
+      <c r="K257" t="s">
+        <v>31</v>
+      </c>
+      <c r="L257" t="s">
+        <v>32</v>
+      </c>
+      <c r="M257" t="s">
+        <v>158</v>
+      </c>
+      <c r="N257" t="str">
+        <f t="shared" si="4"/>
+        <v>213_130</v>
+      </c>
+      <c r="O257" t="s">
+        <v>31</v>
+      </c>
+      <c r="P257" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>31</v>
+      </c>
+      <c r="R257" t="s">
+        <v>31</v>
+      </c>
+      <c r="S257" t="s">
+        <v>31</v>
+      </c>
+      <c r="T257" t="s">
+        <v>31</v>
+      </c>
+      <c r="U257">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A257,B257,C257,D257,E257,F257,G257,H257,I257,J257,K257,L257,M257,N257,O257,P257,Q257,R257,S257,T257)</f>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="258" spans="1:21">
+      <c r="A258" t="b">
+        <v>1</v>
+      </c>
+      <c r="B258" t="s">
+        <v>26</v>
+      </c>
+      <c r="C258" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="E258" t="s">
+        <v>38</v>
+      </c>
+      <c r="F258" t="s">
+        <v>27</v>
+      </c>
+      <c r="G258" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H258" t="s">
+        <v>29</v>
+      </c>
+      <c r="I258" t="s">
+        <v>83</v>
+      </c>
+      <c r="J258" t="s">
+        <v>41</v>
+      </c>
+      <c r="K258" t="s">
+        <v>31</v>
+      </c>
+      <c r="L258" t="s">
+        <v>32</v>
+      </c>
+      <c r="M258" t="s">
+        <v>171</v>
+      </c>
+      <c r="N258" t="str">
+        <f t="shared" si="4"/>
+        <v>111_450</v>
+      </c>
+      <c r="O258" t="s">
+        <v>31</v>
+      </c>
+      <c r="P258" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>31</v>
+      </c>
+      <c r="R258" t="s">
+        <v>31</v>
+      </c>
+      <c r="S258" t="s">
+        <v>31</v>
+      </c>
+      <c r="T258" t="s">
+        <v>31</v>
+      </c>
+      <c r="U258">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A258,B258,C258,D258,E258,F258,G258,H258,I258,J258,K258,L258,M258,N258,O258,P258,Q258,R258,S258,T258)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:21">
+      <c r="A259" t="b">
+        <v>1</v>
+      </c>
+      <c r="B259" t="s">
+        <v>26</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E259" t="s">
+        <v>38</v>
+      </c>
+      <c r="F259" t="s">
+        <v>27</v>
+      </c>
+      <c r="G259" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H259" t="s">
+        <v>29</v>
+      </c>
+      <c r="I259" t="s">
+        <v>83</v>
+      </c>
+      <c r="J259" t="s">
+        <v>41</v>
+      </c>
+      <c r="K259" t="s">
+        <v>31</v>
+      </c>
+      <c r="L259" t="s">
+        <v>32</v>
+      </c>
+      <c r="M259" t="s">
+        <v>172</v>
+      </c>
+      <c r="N259" t="str">
+        <f t="shared" si="4"/>
+        <v>113_104</v>
+      </c>
+      <c r="O259" t="s">
+        <v>31</v>
+      </c>
+      <c r="P259" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>31</v>
+      </c>
+      <c r="R259" t="s">
+        <v>31</v>
+      </c>
+      <c r="S259" t="s">
+        <v>31</v>
+      </c>
+      <c r="T259" t="s">
+        <v>31</v>
+      </c>
+      <c r="U259">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A259,B259,C259,D259,E259,F259,G259,H259,I259,J259,K259,L259,M259,N259,O259,P259,Q259,R259,S259,T259)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:21">
+      <c r="A260" t="b">
+        <v>1</v>
+      </c>
+      <c r="B260" t="s">
+        <v>26</v>
+      </c>
+      <c r="C260" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E260" t="s">
+        <v>38</v>
+      </c>
+      <c r="F260" t="s">
+        <v>27</v>
+      </c>
+      <c r="G260" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H260" t="s">
+        <v>29</v>
+      </c>
+      <c r="I260" t="s">
+        <v>83</v>
+      </c>
+      <c r="J260" t="s">
+        <v>41</v>
+      </c>
+      <c r="K260" t="s">
+        <v>31</v>
+      </c>
+      <c r="L260" t="s">
+        <v>32</v>
+      </c>
+      <c r="M260" t="s">
+        <v>173</v>
+      </c>
+      <c r="N260" t="str">
+        <f t="shared" si="4"/>
+        <v>113_123</v>
+      </c>
+      <c r="O260" t="s">
+        <v>31</v>
+      </c>
+      <c r="P260" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>31</v>
+      </c>
+      <c r="R260" t="s">
+        <v>31</v>
+      </c>
+      <c r="S260" t="s">
+        <v>31</v>
+      </c>
+      <c r="T260" t="s">
+        <v>31</v>
+      </c>
+      <c r="U260">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A260,B260,C260,D260,E260,F260,G260,H260,I260,J260,K260,L260,M260,N260,O260,P260,Q260,R260,S260,T260)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:21">
+      <c r="A261" t="b">
+        <v>1</v>
+      </c>
+      <c r="B261" t="s">
+        <v>26</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E261" t="s">
+        <v>38</v>
+      </c>
+      <c r="F261" t="s">
+        <v>27</v>
+      </c>
+      <c r="G261" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H261" t="s">
+        <v>29</v>
+      </c>
+      <c r="I261" t="s">
+        <v>83</v>
+      </c>
+      <c r="J261" t="s">
+        <v>41</v>
+      </c>
+      <c r="K261" t="s">
+        <v>31</v>
+      </c>
+      <c r="L261" t="s">
+        <v>32</v>
+      </c>
+      <c r="M261" t="s">
+        <v>175</v>
+      </c>
+      <c r="N261" t="str">
+        <f t="shared" si="4"/>
+        <v>900_950</v>
+      </c>
+      <c r="O261" t="s">
+        <v>31</v>
+      </c>
+      <c r="P261" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>31</v>
+      </c>
+      <c r="R261" t="s">
+        <v>31</v>
+      </c>
+      <c r="S261" t="s">
+        <v>31</v>
+      </c>
+      <c r="T261" t="s">
+        <v>31</v>
+      </c>
+      <c r="U261">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A261,B261,C261,D261,E261,F261,G261,H261,I261,J261,K261,L261,M261,N261,O261,P261,Q261,R261,S261,T261)</f>
+        <v>-87577.43</v>
+      </c>
+    </row>
+    <row r="262" spans="1:21">
+      <c r="A262" t="b">
+        <v>1</v>
+      </c>
+      <c r="B262" t="s">
+        <v>26</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E262" t="s">
+        <v>38</v>
+      </c>
+      <c r="F262" t="s">
+        <v>27</v>
+      </c>
+      <c r="G262" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H262" t="s">
+        <v>29</v>
+      </c>
+      <c r="I262" t="s">
+        <v>83</v>
+      </c>
+      <c r="J262" t="s">
+        <v>41</v>
+      </c>
+      <c r="K262" t="s">
+        <v>31</v>
+      </c>
+      <c r="L262" t="s">
+        <v>32</v>
+      </c>
+      <c r="M262" t="s">
+        <v>175</v>
+      </c>
+      <c r="N262" t="str">
+        <f t="shared" si="4"/>
+        <v>905_950</v>
+      </c>
+      <c r="O262" t="s">
+        <v>31</v>
+      </c>
+      <c r="P262" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>31</v>
+      </c>
+      <c r="R262" t="s">
+        <v>31</v>
+      </c>
+      <c r="S262" t="s">
+        <v>31</v>
+      </c>
+      <c r="T262" t="s">
+        <v>31</v>
+      </c>
+      <c r="U262">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A262,B262,C262,D262,E262,F262,G262,H262,I262,J262,K262,L262,M262,N262,O262,P262,Q262,R262,S262,T262)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:21">
+      <c r="A263" t="b">
+        <v>1</v>
+      </c>
+      <c r="B263" t="s">
+        <v>26</v>
+      </c>
+      <c r="C263" t="s">
+        <v>179</v>
+      </c>
+      <c r="E263" t="s">
+        <v>38</v>
+      </c>
+      <c r="F263" t="s">
+        <v>27</v>
+      </c>
+      <c r="G263" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H263" t="s">
+        <v>29</v>
+      </c>
+      <c r="I263" t="s">
+        <v>83</v>
+      </c>
+      <c r="J263" t="s">
+        <v>41</v>
+      </c>
+      <c r="K263" t="s">
+        <v>31</v>
+      </c>
+      <c r="L263" t="s">
+        <v>32</v>
+      </c>
+      <c r="M263" t="s">
+        <v>181</v>
+      </c>
+      <c r="N263" t="str">
+        <f t="shared" ref="N263:N270" si="5">_xlfn.CONCAT(C263,"_",M263)</f>
+        <v>186_520</v>
+      </c>
+      <c r="O263" t="s">
+        <v>31</v>
+      </c>
+      <c r="P263" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>31</v>
+      </c>
+      <c r="R263" t="s">
+        <v>31</v>
+      </c>
+      <c r="S263" t="s">
+        <v>31</v>
+      </c>
+      <c r="T263" t="s">
+        <v>31</v>
+      </c>
+      <c r="U263">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A263,B263,C263,D263,E263,F263,G263,H263,I263,J263,K263,L263,M263,N263,O263,P263,Q263,R263,S263,T263)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:21">
+      <c r="A264" t="b">
+        <v>1</v>
+      </c>
+      <c r="B264" t="s">
+        <v>26</v>
+      </c>
+      <c r="C264" t="s">
+        <v>163</v>
+      </c>
+      <c r="E264" t="s">
+        <v>38</v>
+      </c>
+      <c r="F264" t="s">
+        <v>27</v>
+      </c>
+      <c r="G264" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H264" t="s">
+        <v>29</v>
+      </c>
+      <c r="I264" t="s">
+        <v>83</v>
+      </c>
+      <c r="J264" t="s">
+        <v>41</v>
+      </c>
+      <c r="K264" t="s">
+        <v>31</v>
+      </c>
+      <c r="L264" t="s">
+        <v>32</v>
+      </c>
+      <c r="M264" t="s">
+        <v>182</v>
+      </c>
+      <c r="N264" t="str">
+        <f t="shared" si="5"/>
+        <v>111_380</v>
+      </c>
+      <c r="O264" t="s">
+        <v>31</v>
+      </c>
+      <c r="P264" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>31</v>
+      </c>
+      <c r="R264" t="s">
+        <v>31</v>
+      </c>
+      <c r="S264" t="s">
+        <v>31</v>
+      </c>
+      <c r="T264" t="s">
+        <v>31</v>
+      </c>
+      <c r="U264">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A264,B264,C264,D264,E264,F264,G264,H264,I264,J264,K264,L264,M264,N264,O264,P264,Q264,R264,S264,T264)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:21">
+      <c r="A265" t="b">
+        <v>1</v>
+      </c>
+      <c r="B265" t="s">
+        <v>26</v>
+      </c>
+      <c r="C265" t="s">
+        <v>180</v>
+      </c>
+      <c r="E265" t="s">
+        <v>38</v>
+      </c>
+      <c r="F265" t="s">
+        <v>27</v>
+      </c>
+      <c r="G265" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H265" t="s">
+        <v>29</v>
+      </c>
+      <c r="I265" t="s">
+        <v>83</v>
+      </c>
+      <c r="J265" t="s">
+        <v>41</v>
+      </c>
+      <c r="K265" t="s">
+        <v>31</v>
+      </c>
+      <c r="L265" t="s">
+        <v>32</v>
+      </c>
+      <c r="M265" t="s">
+        <v>182</v>
+      </c>
+      <c r="N265" t="str">
+        <f t="shared" si="5"/>
+        <v>290_380</v>
+      </c>
+      <c r="O265" t="s">
+        <v>31</v>
+      </c>
+      <c r="P265" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>31</v>
+      </c>
+      <c r="R265" t="s">
+        <v>31</v>
+      </c>
+      <c r="S265" t="s">
+        <v>31</v>
+      </c>
+      <c r="T265" t="s">
+        <v>31</v>
+      </c>
+      <c r="U265">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A265,B265,C265,D265,E265,F265,G265,H265,I265,J265,K265,L265,M265,N265,O265,P265,Q265,R265,S265,T265)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:21">
+      <c r="A266" t="b">
+        <v>1</v>
+      </c>
+      <c r="B266" t="s">
+        <v>26</v>
+      </c>
+      <c r="C266" t="s">
+        <v>163</v>
+      </c>
+      <c r="E266" t="s">
+        <v>38</v>
+      </c>
+      <c r="F266" t="s">
+        <v>27</v>
+      </c>
+      <c r="G266" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H266" t="s">
+        <v>29</v>
+      </c>
+      <c r="I266" t="s">
+        <v>83</v>
+      </c>
+      <c r="J266" t="s">
+        <v>41</v>
+      </c>
+      <c r="K266" t="s">
+        <v>31</v>
+      </c>
+      <c r="L266" t="s">
+        <v>32</v>
+      </c>
+      <c r="M266" t="s">
+        <v>183</v>
+      </c>
+      <c r="N266" t="str">
+        <f t="shared" si="5"/>
+        <v>111_105</v>
+      </c>
+      <c r="O266" t="s">
+        <v>31</v>
+      </c>
+      <c r="P266" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>31</v>
+      </c>
+      <c r="R266" t="s">
+        <v>31</v>
+      </c>
+      <c r="S266" t="s">
+        <v>31</v>
+      </c>
+      <c r="T266" t="s">
+        <v>31</v>
+      </c>
+      <c r="U266">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A266,B266,C266,D266,E266,F266,G266,H266,I266,J266,K266,L266,M266,N266,O266,P266,Q266,R266,S266,T266)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:21">
+      <c r="A267" t="b">
+        <v>1</v>
+      </c>
+      <c r="B267" t="s">
+        <v>26</v>
+      </c>
+      <c r="C267" t="s">
+        <v>163</v>
+      </c>
+      <c r="E267" t="s">
+        <v>38</v>
+      </c>
+      <c r="F267" t="s">
+        <v>27</v>
+      </c>
+      <c r="G267" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H267" t="s">
+        <v>29</v>
+      </c>
+      <c r="I267" t="s">
+        <v>83</v>
+      </c>
+      <c r="J267" t="s">
+        <v>41</v>
+      </c>
+      <c r="K267" t="s">
+        <v>31</v>
+      </c>
+      <c r="L267" t="s">
+        <v>32</v>
+      </c>
+      <c r="M267" t="s">
+        <v>184</v>
+      </c>
+      <c r="N267" t="str">
+        <f t="shared" si="5"/>
+        <v>111_304</v>
+      </c>
+      <c r="O267" t="s">
+        <v>31</v>
+      </c>
+      <c r="P267" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>31</v>
+      </c>
+      <c r="R267" t="s">
+        <v>31</v>
+      </c>
+      <c r="S267" t="s">
+        <v>31</v>
+      </c>
+      <c r="T267" t="s">
+        <v>31</v>
+      </c>
+      <c r="U267">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A267,B267,C267,D267,E267,F267,G267,H267,I267,J267,K267,L267,M267,N267,O267,P267,Q267,R267,S267,T267)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:21">
+      <c r="A268" t="b">
+        <v>1</v>
+      </c>
+      <c r="B268" t="s">
+        <v>26</v>
+      </c>
+      <c r="C268" t="s">
+        <v>151</v>
+      </c>
+      <c r="E268" t="s">
+        <v>38</v>
+      </c>
+      <c r="F268" t="s">
+        <v>27</v>
+      </c>
+      <c r="G268" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H268" t="s">
+        <v>29</v>
+      </c>
+      <c r="I268" t="s">
+        <v>83</v>
+      </c>
+      <c r="J268" t="s">
+        <v>41</v>
+      </c>
+      <c r="K268" t="s">
+        <v>31</v>
+      </c>
+      <c r="L268" t="s">
+        <v>32</v>
+      </c>
+      <c r="M268" t="s">
+        <v>185</v>
+      </c>
+      <c r="N268" t="str">
+        <f t="shared" si="5"/>
+        <v>113_501</v>
+      </c>
+      <c r="O268" t="s">
+        <v>31</v>
+      </c>
+      <c r="P268" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>31</v>
+      </c>
+      <c r="R268" t="s">
+        <v>31</v>
+      </c>
+      <c r="S268" t="s">
+        <v>31</v>
+      </c>
+      <c r="T268" t="s">
+        <v>31</v>
+      </c>
+      <c r="U268">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A268,B268,C268,D268,E268,F268,G268,H268,I268,J268,K268,L268,M268,N268,O268,P268,Q268,R268,S268,T268)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:21">
+      <c r="A269" t="b">
+        <v>1</v>
+      </c>
+      <c r="B269" t="s">
+        <v>26</v>
+      </c>
+      <c r="C269" t="s">
+        <v>151</v>
+      </c>
+      <c r="E269" t="s">
+        <v>38</v>
+      </c>
+      <c r="F269" t="s">
+        <v>27</v>
+      </c>
+      <c r="G269" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H269" t="s">
+        <v>29</v>
+      </c>
+      <c r="I269" t="s">
+        <v>83</v>
+      </c>
+      <c r="J269" t="s">
+        <v>41</v>
+      </c>
+      <c r="K269" t="s">
+        <v>31</v>
+      </c>
+      <c r="L269" t="s">
+        <v>32</v>
+      </c>
+      <c r="M269" t="s">
+        <v>186</v>
+      </c>
+      <c r="N269" t="str">
+        <f t="shared" si="5"/>
+        <v>113_500</v>
+      </c>
+      <c r="O269" t="s">
+        <v>31</v>
+      </c>
+      <c r="P269" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>31</v>
+      </c>
+      <c r="R269" t="s">
+        <v>31</v>
+      </c>
+      <c r="S269" t="s">
+        <v>31</v>
+      </c>
+      <c r="T269" t="s">
+        <v>31</v>
+      </c>
+      <c r="U269">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A269,B269,C269,D269,E269,F269,G269,H269,I269,J269,K269,L269,M269,N269,O269,P269,Q269,R269,S269,T269)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:21">
+      <c r="A270" t="b">
+        <v>1</v>
+      </c>
+      <c r="B270" t="s">
+        <v>26</v>
+      </c>
+      <c r="C270" t="s">
+        <v>151</v>
+      </c>
+      <c r="E270" t="s">
+        <v>38</v>
+      </c>
+      <c r="F270" t="s">
+        <v>27</v>
+      </c>
+      <c r="G270" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H270" t="s">
+        <v>29</v>
+      </c>
+      <c r="I270" t="s">
+        <v>83</v>
+      </c>
+      <c r="J270" t="s">
+        <v>41</v>
+      </c>
+      <c r="K270" t="s">
+        <v>31</v>
+      </c>
+      <c r="L270" t="s">
+        <v>32</v>
+      </c>
+      <c r="M270" t="s">
+        <v>187</v>
+      </c>
+      <c r="N270" t="str">
+        <f t="shared" si="5"/>
+        <v>113_525</v>
+      </c>
+      <c r="O270" t="s">
+        <v>31</v>
+      </c>
+      <c r="P270" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>31</v>
+      </c>
+      <c r="R270" t="s">
+        <v>31</v>
+      </c>
+      <c r="S270" t="s">
+        <v>31</v>
+      </c>
+      <c r="T270" t="s">
+        <v>31</v>
+      </c>
+      <c r="U270">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A270,B270,C270,D270,E270,F270,G270,H270,I270,J270,K270,L270,M270,N270,O270,P270,Q270,R270,S270,T270)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:21">
+      <c r="A271" t="b">
+        <v>1</v>
+      </c>
+      <c r="B271" t="s">
+        <v>26</v>
+      </c>
+      <c r="C271" t="s">
+        <v>151</v>
+      </c>
+      <c r="E271" t="s">
+        <v>38</v>
+      </c>
+      <c r="F271" t="s">
+        <v>27</v>
+      </c>
+      <c r="G271" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H271" t="s">
+        <v>29</v>
+      </c>
+      <c r="I271" t="s">
+        <v>83</v>
+      </c>
+      <c r="J271" t="s">
+        <v>41</v>
+      </c>
+      <c r="K271" t="s">
+        <v>31</v>
+      </c>
+      <c r="L271" t="s">
+        <v>32</v>
+      </c>
+      <c r="M271" t="s">
+        <v>193</v>
+      </c>
+      <c r="N271" t="str">
+        <f t="shared" ref="N271:N299" si="6">_xlfn.CONCAT(C271,"_",M271)</f>
+        <v>113_110</v>
+      </c>
+      <c r="O271" t="s">
+        <v>31</v>
+      </c>
+      <c r="P271" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>31</v>
+      </c>
+      <c r="R271" t="s">
+        <v>31</v>
+      </c>
+      <c r="S271" t="s">
+        <v>31</v>
+      </c>
+      <c r="T271" t="s">
+        <v>31</v>
+      </c>
+      <c r="U271">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A271,B271,C271,D271,E271,F271,G271,H271,I271,J271,K271,L271,M271,N271,O271,P271,Q271,R271,S271,T271)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:21">
+      <c r="A272" t="b">
+        <v>1</v>
+      </c>
+      <c r="B272" t="s">
+        <v>26</v>
+      </c>
+      <c r="C272" t="s">
+        <v>163</v>
+      </c>
+      <c r="E272" t="s">
+        <v>38</v>
+      </c>
+      <c r="F272" t="s">
+        <v>27</v>
+      </c>
+      <c r="G272" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H272" t="s">
+        <v>29</v>
+      </c>
+      <c r="I272" t="s">
+        <v>83</v>
+      </c>
+      <c r="J272" t="s">
+        <v>41</v>
+      </c>
+      <c r="K272" t="s">
+        <v>31</v>
+      </c>
+      <c r="L272" t="s">
+        <v>32</v>
+      </c>
+      <c r="M272" t="s">
+        <v>194</v>
+      </c>
+      <c r="N272" t="str">
+        <f t="shared" si="6"/>
+        <v>111_175</v>
+      </c>
+      <c r="O272" t="s">
+        <v>31</v>
+      </c>
+      <c r="P272" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>31</v>
+      </c>
+      <c r="R272" t="s">
+        <v>31</v>
+      </c>
+      <c r="S272" t="s">
+        <v>31</v>
+      </c>
+      <c r="T272" t="s">
+        <v>31</v>
+      </c>
+      <c r="U272">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A272,B272,C272,D272,E272,F272,G272,H272,I272,J272,K272,L272,M272,N272,O272,P272,Q272,R272,S272,T272)</f>
+        <v>142.28</v>
+      </c>
+    </row>
+    <row r="273" spans="1:21">
+      <c r="A273" t="b">
+        <v>1</v>
+      </c>
+      <c r="B273" t="s">
+        <v>26</v>
+      </c>
+      <c r="C273" t="s">
+        <v>151</v>
+      </c>
+      <c r="E273" t="s">
+        <v>38</v>
+      </c>
+      <c r="F273" t="s">
+        <v>27</v>
+      </c>
+      <c r="G273" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H273" t="s">
+        <v>29</v>
+      </c>
+      <c r="I273" t="s">
+        <v>83</v>
+      </c>
+      <c r="J273" t="s">
+        <v>41</v>
+      </c>
+      <c r="K273" t="s">
+        <v>31</v>
+      </c>
+      <c r="L273" t="s">
+        <v>32</v>
+      </c>
+      <c r="M273" t="s">
+        <v>195</v>
+      </c>
+      <c r="N273" t="str">
+        <f t="shared" si="6"/>
+        <v>113_513</v>
+      </c>
+      <c r="O273" t="s">
+        <v>31</v>
+      </c>
+      <c r="P273" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>31</v>
+      </c>
+      <c r="R273" t="s">
+        <v>31</v>
+      </c>
+      <c r="S273" t="s">
+        <v>31</v>
+      </c>
+      <c r="T273" t="s">
+        <v>31</v>
+      </c>
+      <c r="U273">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A273,B273,C273,D273,E273,F273,G273,H273,I273,J273,K273,L273,M273,N273,O273,P273,Q273,R273,S273,T273)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:21">
+      <c r="A274" t="b">
+        <v>1</v>
+      </c>
+      <c r="B274" t="s">
+        <v>26</v>
+      </c>
+      <c r="C274" t="s">
+        <v>151</v>
+      </c>
+      <c r="E274" t="s">
+        <v>38</v>
+      </c>
+      <c r="F274" t="s">
+        <v>27</v>
+      </c>
+      <c r="G274" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H274" t="s">
+        <v>29</v>
+      </c>
+      <c r="I274" t="s">
+        <v>83</v>
+      </c>
+      <c r="J274" t="s">
+        <v>41</v>
+      </c>
+      <c r="K274" t="s">
+        <v>31</v>
+      </c>
+      <c r="L274" t="s">
+        <v>32</v>
+      </c>
+      <c r="M274" t="s">
+        <v>196</v>
+      </c>
+      <c r="N274" t="str">
+        <f t="shared" si="6"/>
+        <v>113_519</v>
+      </c>
+      <c r="O274" t="s">
+        <v>31</v>
+      </c>
+      <c r="P274" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>31</v>
+      </c>
+      <c r="R274" t="s">
+        <v>31</v>
+      </c>
+      <c r="S274" t="s">
+        <v>31</v>
+      </c>
+      <c r="T274" t="s">
+        <v>31</v>
+      </c>
+      <c r="U274">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A274,B274,C274,D274,E274,F274,G274,H274,I274,J274,K274,L274,M274,N274,O274,P274,Q274,R274,S274,T274)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:21">
+      <c r="A275" t="b">
+        <v>1</v>
+      </c>
+      <c r="B275" t="s">
+        <v>26</v>
+      </c>
+      <c r="C275" t="s">
+        <v>151</v>
+      </c>
+      <c r="E275" t="s">
+        <v>38</v>
+      </c>
+      <c r="F275" t="s">
+        <v>27</v>
+      </c>
+      <c r="G275" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H275" t="s">
+        <v>29</v>
+      </c>
+      <c r="I275" t="s">
+        <v>83</v>
+      </c>
+      <c r="J275" t="s">
+        <v>41</v>
+      </c>
+      <c r="K275" t="s">
+        <v>31</v>
+      </c>
+      <c r="L275" t="s">
+        <v>32</v>
+      </c>
+      <c r="M275" t="s">
+        <v>197</v>
+      </c>
+      <c r="N275" t="str">
+        <f t="shared" si="6"/>
+        <v>113_515</v>
+      </c>
+      <c r="O275" t="s">
+        <v>31</v>
+      </c>
+      <c r="P275" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>31</v>
+      </c>
+      <c r="R275" t="s">
+        <v>31</v>
+      </c>
+      <c r="S275" t="s">
+        <v>31</v>
+      </c>
+      <c r="T275" t="s">
+        <v>31</v>
+      </c>
+      <c r="U275">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A275,B275,C275,D275,E275,F275,G275,H275,I275,J275,K275,L275,M275,N275,O275,P275,Q275,R275,S275,T275)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:21">
+      <c r="A276" t="b">
+        <v>1</v>
+      </c>
+      <c r="B276" t="s">
+        <v>26</v>
+      </c>
+      <c r="C276" t="s">
+        <v>151</v>
+      </c>
+      <c r="E276" t="s">
+        <v>38</v>
+      </c>
+      <c r="F276" t="s">
+        <v>27</v>
+      </c>
+      <c r="G276" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H276" t="s">
+        <v>29</v>
+      </c>
+      <c r="I276" t="s">
+        <v>83</v>
+      </c>
+      <c r="J276" t="s">
+        <v>41</v>
+      </c>
+      <c r="K276" t="s">
+        <v>31</v>
+      </c>
+      <c r="L276" t="s">
+        <v>32</v>
+      </c>
+      <c r="M276" t="s">
+        <v>198</v>
+      </c>
+      <c r="N276" t="str">
+        <f t="shared" si="6"/>
+        <v>113_510</v>
+      </c>
+      <c r="O276" t="s">
+        <v>31</v>
+      </c>
+      <c r="P276" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>31</v>
+      </c>
+      <c r="R276" t="s">
+        <v>31</v>
+      </c>
+      <c r="S276" t="s">
+        <v>31</v>
+      </c>
+      <c r="T276" t="s">
+        <v>31</v>
+      </c>
+      <c r="U276">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A276,B276,C276,D276,E276,F276,G276,H276,I276,J276,K276,L276,M276,N276,O276,P276,Q276,R276,S276,T276)</f>
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="277" spans="1:21">
+      <c r="A277" t="b">
+        <v>1</v>
+      </c>
+      <c r="B277" t="s">
+        <v>26</v>
+      </c>
+      <c r="C277" t="s">
+        <v>151</v>
+      </c>
+      <c r="E277" t="s">
+        <v>38</v>
+      </c>
+      <c r="F277" t="s">
+        <v>27</v>
+      </c>
+      <c r="G277" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H277" t="s">
+        <v>29</v>
+      </c>
+      <c r="I277" t="s">
+        <v>83</v>
+      </c>
+      <c r="J277" t="s">
+        <v>41</v>
+      </c>
+      <c r="K277" t="s">
+        <v>31</v>
+      </c>
+      <c r="L277" t="s">
+        <v>32</v>
+      </c>
+      <c r="M277" t="s">
+        <v>199</v>
+      </c>
+      <c r="N277" t="str">
+        <f t="shared" si="6"/>
+        <v>113_518</v>
+      </c>
+      <c r="O277" t="s">
+        <v>31</v>
+      </c>
+      <c r="P277" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>31</v>
+      </c>
+      <c r="R277" t="s">
+        <v>31</v>
+      </c>
+      <c r="S277" t="s">
+        <v>31</v>
+      </c>
+      <c r="T277" t="s">
+        <v>31</v>
+      </c>
+      <c r="U277">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A277,B277,C277,D277,E277,F277,G277,H277,I277,J277,K277,L277,M277,N277,O277,P277,Q277,R277,S277,T277)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:21">
+      <c r="A278" t="b">
+        <v>1</v>
+      </c>
+      <c r="B278" t="s">
+        <v>26</v>
+      </c>
+      <c r="C278" t="s">
+        <v>163</v>
+      </c>
+      <c r="E278" t="s">
+        <v>38</v>
+      </c>
+      <c r="F278" t="s">
+        <v>27</v>
+      </c>
+      <c r="G278" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H278" t="s">
+        <v>29</v>
+      </c>
+      <c r="I278" t="s">
+        <v>83</v>
+      </c>
+      <c r="J278" t="s">
+        <v>41</v>
+      </c>
+      <c r="K278" t="s">
+        <v>31</v>
+      </c>
+      <c r="L278" t="s">
+        <v>32</v>
+      </c>
+      <c r="M278" t="s">
+        <v>167</v>
+      </c>
+      <c r="N278" t="str">
+        <f t="shared" si="6"/>
+        <v>111_307</v>
+      </c>
+      <c r="O278" t="s">
+        <v>31</v>
+      </c>
+      <c r="P278" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>31</v>
+      </c>
+      <c r="R278" t="s">
+        <v>31</v>
+      </c>
+      <c r="S278" t="s">
+        <v>31</v>
+      </c>
+      <c r="T278" t="s">
+        <v>31</v>
+      </c>
+      <c r="U278">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A278,B278,C278,D278,E278,F278,G278,H278,I278,J278,K278,L278,M278,N278,O278,P278,Q278,R278,S278,T278)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:21">
+      <c r="A279" t="b">
+        <v>1</v>
+      </c>
+      <c r="B279" t="s">
+        <v>26</v>
+      </c>
+      <c r="C279" t="s">
+        <v>151</v>
+      </c>
+      <c r="E279" t="s">
+        <v>38</v>
+      </c>
+      <c r="F279" t="s">
+        <v>27</v>
+      </c>
+      <c r="G279" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H279" t="s">
+        <v>29</v>
+      </c>
+      <c r="I279" t="s">
+        <v>83</v>
+      </c>
+      <c r="J279" t="s">
+        <v>41</v>
+      </c>
+      <c r="K279" t="s">
+        <v>31</v>
+      </c>
+      <c r="L279" t="s">
+        <v>32</v>
+      </c>
+      <c r="M279" t="s">
+        <v>200</v>
+      </c>
+      <c r="N279" t="str">
+        <f t="shared" si="6"/>
+        <v>113_517</v>
+      </c>
+      <c r="O279" t="s">
+        <v>31</v>
+      </c>
+      <c r="P279" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>31</v>
+      </c>
+      <c r="R279" t="s">
+        <v>31</v>
+      </c>
+      <c r="S279" t="s">
+        <v>31</v>
+      </c>
+      <c r="T279" t="s">
+        <v>31</v>
+      </c>
+      <c r="U279">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A279,B279,C279,D279,E279,F279,G279,H279,I279,J279,K279,L279,M279,N279,O279,P279,Q279,R279,S279,T279)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:21">
+      <c r="A280" t="b">
+        <v>1</v>
+      </c>
+      <c r="B280" t="s">
+        <v>26</v>
+      </c>
+      <c r="C280" t="s">
+        <v>163</v>
+      </c>
+      <c r="E280" t="s">
+        <v>38</v>
+      </c>
+      <c r="F280" t="s">
+        <v>27</v>
+      </c>
+      <c r="G280" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H280" t="s">
+        <v>29</v>
+      </c>
+      <c r="I280" t="s">
+        <v>83</v>
+      </c>
+      <c r="J280" t="s">
+        <v>41</v>
+      </c>
+      <c r="K280" t="s">
+        <v>31</v>
+      </c>
+      <c r="L280" t="s">
+        <v>32</v>
+      </c>
+      <c r="M280" t="s">
+        <v>201</v>
+      </c>
+      <c r="N280" t="str">
+        <f t="shared" si="6"/>
+        <v>111_350</v>
+      </c>
+      <c r="O280" t="s">
+        <v>31</v>
+      </c>
+      <c r="P280" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>31</v>
+      </c>
+      <c r="R280" t="s">
+        <v>31</v>
+      </c>
+      <c r="S280" t="s">
+        <v>31</v>
+      </c>
+      <c r="T280" t="s">
+        <v>31</v>
+      </c>
+      <c r="U280">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A280,B280,C280,D280,E280,F280,G280,H280,I280,J280,K280,L280,M280,N280,O280,P280,Q280,R280,S280,T280)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:21">
+      <c r="A281" t="b">
+        <v>1</v>
+      </c>
+      <c r="B281" t="s">
+        <v>26</v>
+      </c>
+      <c r="C281" t="s">
+        <v>188</v>
+      </c>
+      <c r="E281" t="s">
+        <v>38</v>
+      </c>
+      <c r="F281" t="s">
+        <v>27</v>
+      </c>
+      <c r="G281" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H281" t="s">
+        <v>29</v>
+      </c>
+      <c r="I281" t="s">
+        <v>83</v>
+      </c>
+      <c r="J281" t="s">
+        <v>41</v>
+      </c>
+      <c r="K281" t="s">
+        <v>31</v>
+      </c>
+      <c r="L281" t="s">
+        <v>32</v>
+      </c>
+      <c r="M281" t="s">
+        <v>202</v>
+      </c>
+      <c r="N281" t="str">
+        <f t="shared" si="6"/>
+        <v>289_351</v>
+      </c>
+      <c r="O281" t="s">
+        <v>31</v>
+      </c>
+      <c r="P281" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>31</v>
+      </c>
+      <c r="R281" t="s">
+        <v>31</v>
+      </c>
+      <c r="S281" t="s">
+        <v>31</v>
+      </c>
+      <c r="T281" t="s">
+        <v>31</v>
+      </c>
+      <c r="U281">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A281,B281,C281,D281,E281,F281,G281,H281,I281,J281,K281,L281,M281,N281,O281,P281,Q281,R281,S281,T281)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:21">
+      <c r="A282" t="b">
+        <v>1</v>
+      </c>
+      <c r="B282" t="s">
+        <v>26</v>
+      </c>
+      <c r="C282" t="s">
+        <v>163</v>
+      </c>
+      <c r="E282" t="s">
+        <v>38</v>
+      </c>
+      <c r="F282" t="s">
+        <v>27</v>
+      </c>
+      <c r="G282" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H282" t="s">
+        <v>29</v>
+      </c>
+      <c r="I282" t="s">
+        <v>83</v>
+      </c>
+      <c r="J282" t="s">
+        <v>41</v>
+      </c>
+      <c r="K282" t="s">
+        <v>31</v>
+      </c>
+      <c r="L282" t="s">
+        <v>32</v>
+      </c>
+      <c r="M282" t="s">
+        <v>203</v>
+      </c>
+      <c r="N282" t="str">
+        <f t="shared" si="6"/>
+        <v>111_360</v>
+      </c>
+      <c r="O282" t="s">
+        <v>31</v>
+      </c>
+      <c r="P282" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q282" t="s">
+        <v>31</v>
+      </c>
+      <c r="R282" t="s">
+        <v>31</v>
+      </c>
+      <c r="S282" t="s">
+        <v>31</v>
+      </c>
+      <c r="T282" t="s">
+        <v>31</v>
+      </c>
+      <c r="U282">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A282,B282,C282,D282,E282,F282,G282,H282,I282,J282,K282,L282,M282,N282,O282,P282,Q282,R282,S282,T282)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:21">
+      <c r="A283" t="b">
+        <v>1</v>
+      </c>
+      <c r="B283" t="s">
+        <v>26</v>
+      </c>
+      <c r="C283" t="s">
+        <v>163</v>
+      </c>
+      <c r="E283" t="s">
+        <v>38</v>
+      </c>
+      <c r="F283" t="s">
+        <v>27</v>
+      </c>
+      <c r="G283" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H283" t="s">
+        <v>29</v>
+      </c>
+      <c r="I283" t="s">
+        <v>83</v>
+      </c>
+      <c r="J283" t="s">
+        <v>41</v>
+      </c>
+      <c r="K283" t="s">
+        <v>31</v>
+      </c>
+      <c r="L283" t="s">
+        <v>32</v>
+      </c>
+      <c r="M283" t="s">
+        <v>204</v>
+      </c>
+      <c r="N283" t="str">
+        <f t="shared" si="6"/>
+        <v>111_366</v>
+      </c>
+      <c r="O283" t="s">
+        <v>31</v>
+      </c>
+      <c r="P283" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q283" t="s">
+        <v>31</v>
+      </c>
+      <c r="R283" t="s">
+        <v>31</v>
+      </c>
+      <c r="S283" t="s">
+        <v>31</v>
+      </c>
+      <c r="T283" t="s">
+        <v>31</v>
+      </c>
+      <c r="U283">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A283,B283,C283,D283,E283,F283,G283,H283,I283,J283,K283,L283,M283,N283,O283,P283,Q283,R283,S283,T283)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:21">
+      <c r="A284" t="b">
+        <v>1</v>
+      </c>
+      <c r="B284" t="s">
+        <v>26</v>
+      </c>
+      <c r="C284" t="s">
+        <v>163</v>
+      </c>
+      <c r="E284" t="s">
+        <v>38</v>
+      </c>
+      <c r="F284" t="s">
+        <v>27</v>
+      </c>
+      <c r="G284" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H284" t="s">
+        <v>29</v>
+      </c>
+      <c r="I284" t="s">
+        <v>83</v>
+      </c>
+      <c r="J284" t="s">
+        <v>41</v>
+      </c>
+      <c r="K284" t="s">
+        <v>31</v>
+      </c>
+      <c r="L284" t="s">
+        <v>32</v>
+      </c>
+      <c r="M284" t="s">
+        <v>205</v>
+      </c>
+      <c r="N284" t="str">
+        <f t="shared" si="6"/>
+        <v>111_370</v>
+      </c>
+      <c r="O284" t="s">
+        <v>31</v>
+      </c>
+      <c r="P284" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q284" t="s">
+        <v>31</v>
+      </c>
+      <c r="R284" t="s">
+        <v>31</v>
+      </c>
+      <c r="S284" t="s">
+        <v>31</v>
+      </c>
+      <c r="T284" t="s">
+        <v>31</v>
+      </c>
+      <c r="U284">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A284,B284,C284,D284,E284,F284,G284,H284,I284,J284,K284,L284,M284,N284,O284,P284,Q284,R284,S284,T284)</f>
+        <v>547339</v>
+      </c>
+    </row>
+    <row r="285" spans="1:21">
+      <c r="A285" t="b">
+        <v>1</v>
+      </c>
+      <c r="B285" t="s">
+        <v>26</v>
+      </c>
+      <c r="C285" t="s">
+        <v>163</v>
+      </c>
+      <c r="E285" t="s">
+        <v>38</v>
+      </c>
+      <c r="F285" t="s">
+        <v>27</v>
+      </c>
+      <c r="G285" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H285" t="s">
+        <v>29</v>
+      </c>
+      <c r="I285" t="s">
+        <v>83</v>
+      </c>
+      <c r="J285" t="s">
+        <v>41</v>
+      </c>
+      <c r="K285" t="s">
+        <v>31</v>
+      </c>
+      <c r="L285" t="s">
+        <v>32</v>
+      </c>
+      <c r="M285" t="s">
+        <v>206</v>
+      </c>
+      <c r="N285" t="str">
+        <f t="shared" si="6"/>
+        <v>111_301</v>
+      </c>
+      <c r="O285" t="s">
+        <v>31</v>
+      </c>
+      <c r="P285" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q285" t="s">
+        <v>31</v>
+      </c>
+      <c r="R285" t="s">
+        <v>31</v>
+      </c>
+      <c r="S285" t="s">
+        <v>31</v>
+      </c>
+      <c r="T285" t="s">
+        <v>31</v>
+      </c>
+      <c r="U285">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A285,B285,C285,D285,E285,F285,G285,H285,I285,J285,K285,L285,M285,N285,O285,P285,Q285,R285,S285,T285)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:21">
+      <c r="A286" t="b">
+        <v>1</v>
+      </c>
+      <c r="B286" t="s">
+        <v>26</v>
+      </c>
+      <c r="C286" t="s">
+        <v>163</v>
+      </c>
+      <c r="E286" t="s">
+        <v>38</v>
+      </c>
+      <c r="F286" t="s">
+        <v>27</v>
+      </c>
+      <c r="G286" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H286" t="s">
+        <v>29</v>
+      </c>
+      <c r="I286" t="s">
+        <v>83</v>
+      </c>
+      <c r="J286" t="s">
+        <v>41</v>
+      </c>
+      <c r="K286" t="s">
+        <v>31</v>
+      </c>
+      <c r="L286" t="s">
+        <v>32</v>
+      </c>
+      <c r="M286" t="s">
+        <v>207</v>
+      </c>
+      <c r="N286" t="str">
+        <f t="shared" si="6"/>
+        <v>111_308</v>
+      </c>
+      <c r="O286" t="s">
+        <v>31</v>
+      </c>
+      <c r="P286" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q286" t="s">
+        <v>31</v>
+      </c>
+      <c r="R286" t="s">
+        <v>31</v>
+      </c>
+      <c r="S286" t="s">
+        <v>31</v>
+      </c>
+      <c r="T286" t="s">
+        <v>31</v>
+      </c>
+      <c r="U286">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A286,B286,C286,D286,E286,F286,G286,H286,I286,J286,K286,L286,M286,N286,O286,P286,Q286,R286,S286,T286)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:21">
+      <c r="A287" t="b">
+        <v>1</v>
+      </c>
+      <c r="B287" t="s">
+        <v>26</v>
+      </c>
+      <c r="C287" t="s">
+        <v>161</v>
+      </c>
+      <c r="E287" t="s">
+        <v>38</v>
+      </c>
+      <c r="F287" t="s">
+        <v>27</v>
+      </c>
+      <c r="G287" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H287" t="s">
+        <v>29</v>
+      </c>
+      <c r="I287" t="s">
+        <v>83</v>
+      </c>
+      <c r="J287" t="s">
+        <v>41</v>
+      </c>
+      <c r="K287" t="s">
+        <v>31</v>
+      </c>
+      <c r="L287" t="s">
+        <v>32</v>
+      </c>
+      <c r="M287" t="s">
+        <v>208</v>
+      </c>
+      <c r="N287" t="str">
+        <f t="shared" si="6"/>
+        <v>115_845</v>
+      </c>
+      <c r="O287" t="s">
+        <v>31</v>
+      </c>
+      <c r="P287" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q287" t="s">
+        <v>31</v>
+      </c>
+      <c r="R287" t="s">
+        <v>31</v>
+      </c>
+      <c r="S287" t="s">
+        <v>31</v>
+      </c>
+      <c r="T287" t="s">
+        <v>31</v>
+      </c>
+      <c r="U287">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A287,B287,C287,D287,E287,F287,G287,H287,I287,J287,K287,L287,M287,N287,O287,P287,Q287,R287,S287,T287)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:21">
+      <c r="A288" t="b">
+        <v>1</v>
+      </c>
+      <c r="B288" t="s">
+        <v>26</v>
+      </c>
+      <c r="C288" t="s">
+        <v>189</v>
+      </c>
+      <c r="E288" t="s">
+        <v>38</v>
+      </c>
+      <c r="F288" t="s">
+        <v>27</v>
+      </c>
+      <c r="G288" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H288" t="s">
+        <v>29</v>
+      </c>
+      <c r="I288" t="s">
+        <v>83</v>
+      </c>
+      <c r="J288" t="s">
+        <v>41</v>
+      </c>
+      <c r="K288" t="s">
+        <v>31</v>
+      </c>
+      <c r="L288" t="s">
+        <v>32</v>
+      </c>
+      <c r="M288" t="s">
+        <v>177</v>
+      </c>
+      <c r="N288" t="str">
+        <f t="shared" si="6"/>
+        <v>340_170</v>
+      </c>
+      <c r="O288" t="s">
+        <v>31</v>
+      </c>
+      <c r="P288" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q288" t="s">
+        <v>31</v>
+      </c>
+      <c r="R288" t="s">
+        <v>31</v>
+      </c>
+      <c r="S288" t="s">
+        <v>31</v>
+      </c>
+      <c r="T288" t="s">
+        <v>31</v>
+      </c>
+      <c r="U288">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A288,B288,C288,D288,E288,F288,G288,H288,I288,J288,K288,L288,M288,N288,O288,P288,Q288,R288,S288,T288)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:21">
+      <c r="A289" t="b">
+        <v>1</v>
+      </c>
+      <c r="B289" t="s">
+        <v>26</v>
+      </c>
+      <c r="C289" t="s">
+        <v>189</v>
+      </c>
+      <c r="E289" t="s">
+        <v>38</v>
+      </c>
+      <c r="F289" t="s">
+        <v>27</v>
+      </c>
+      <c r="G289" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H289" t="s">
+        <v>29</v>
+      </c>
+      <c r="I289" t="s">
+        <v>83</v>
+      </c>
+      <c r="J289" t="s">
+        <v>41</v>
+      </c>
+      <c r="K289" t="s">
+        <v>31</v>
+      </c>
+      <c r="L289" t="s">
+        <v>32</v>
+      </c>
+      <c r="M289" t="s">
+        <v>194</v>
+      </c>
+      <c r="N289" t="str">
+        <f t="shared" si="6"/>
+        <v>340_175</v>
+      </c>
+      <c r="O289" t="s">
+        <v>31</v>
+      </c>
+      <c r="P289" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q289" t="s">
+        <v>31</v>
+      </c>
+      <c r="R289" t="s">
+        <v>31</v>
+      </c>
+      <c r="S289" t="s">
+        <v>31</v>
+      </c>
+      <c r="T289" t="s">
+        <v>31</v>
+      </c>
+      <c r="U289">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A289,B289,C289,D289,E289,F289,G289,H289,I289,J289,K289,L289,M289,N289,O289,P289,Q289,R289,S289,T289)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:21">
+      <c r="A290" t="b">
+        <v>1</v>
+      </c>
+      <c r="B290" t="s">
+        <v>26</v>
+      </c>
+      <c r="C290" t="s">
+        <v>190</v>
+      </c>
+      <c r="E290" t="s">
+        <v>38</v>
+      </c>
+      <c r="F290" t="s">
+        <v>27</v>
+      </c>
+      <c r="G290" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H290" t="s">
+        <v>29</v>
+      </c>
+      <c r="I290" t="s">
+        <v>83</v>
+      </c>
+      <c r="J290" t="s">
+        <v>41</v>
+      </c>
+      <c r="K290" t="s">
+        <v>31</v>
+      </c>
+      <c r="L290" t="s">
+        <v>32</v>
+      </c>
+      <c r="M290" t="s">
+        <v>209</v>
+      </c>
+      <c r="N290" t="str">
+        <f t="shared" si="6"/>
+        <v>323_723</v>
+      </c>
+      <c r="O290" t="s">
+        <v>31</v>
+      </c>
+      <c r="P290" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q290" t="s">
+        <v>31</v>
+      </c>
+      <c r="R290" t="s">
+        <v>31</v>
+      </c>
+      <c r="S290" t="s">
+        <v>31</v>
+      </c>
+      <c r="T290" t="s">
+        <v>31</v>
+      </c>
+      <c r="U290">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A290,B290,C290,D290,E290,F290,G290,H290,I290,J290,K290,L290,M290,N290,O290,P290,Q290,R290,S290,T290)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:21">
+      <c r="A291" t="b">
+        <v>1</v>
+      </c>
+      <c r="B291" t="s">
+        <v>26</v>
+      </c>
+      <c r="C291" t="s">
+        <v>190</v>
+      </c>
+      <c r="E291" t="s">
+        <v>38</v>
+      </c>
+      <c r="F291" t="s">
+        <v>27</v>
+      </c>
+      <c r="G291" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H291" t="s">
+        <v>29</v>
+      </c>
+      <c r="I291" t="s">
+        <v>83</v>
+      </c>
+      <c r="J291" t="s">
+        <v>41</v>
+      </c>
+      <c r="K291" t="s">
+        <v>31</v>
+      </c>
+      <c r="L291" t="s">
+        <v>32</v>
+      </c>
+      <c r="M291" t="s">
+        <v>210</v>
+      </c>
+      <c r="N291" t="str">
+        <f t="shared" si="6"/>
+        <v>323_720</v>
+      </c>
+      <c r="O291" t="s">
+        <v>31</v>
+      </c>
+      <c r="P291" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q291" t="s">
+        <v>31</v>
+      </c>
+      <c r="R291" t="s">
+        <v>31</v>
+      </c>
+      <c r="S291" t="s">
+        <v>31</v>
+      </c>
+      <c r="T291" t="s">
+        <v>31</v>
+      </c>
+      <c r="U291">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A291,B291,C291,D291,E291,F291,G291,H291,I291,J291,K291,L291,M291,N291,O291,P291,Q291,R291,S291,T291)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:21">
+      <c r="A292" t="b">
+        <v>1</v>
+      </c>
+      <c r="B292" t="s">
+        <v>26</v>
+      </c>
+      <c r="C292" t="s">
+        <v>163</v>
+      </c>
+      <c r="E292" t="s">
+        <v>38</v>
+      </c>
+      <c r="F292" t="s">
+        <v>27</v>
+      </c>
+      <c r="G292" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H292" t="s">
+        <v>29</v>
+      </c>
+      <c r="I292" t="s">
+        <v>83</v>
+      </c>
+      <c r="J292" t="s">
+        <v>41</v>
+      </c>
+      <c r="K292" t="s">
+        <v>31</v>
+      </c>
+      <c r="L292" t="s">
+        <v>32</v>
+      </c>
+      <c r="M292" t="s">
+        <v>211</v>
+      </c>
+      <c r="N292" t="str">
+        <f t="shared" si="6"/>
+        <v>111_302</v>
+      </c>
+      <c r="O292" t="s">
+        <v>31</v>
+      </c>
+      <c r="P292" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q292" t="s">
+        <v>31</v>
+      </c>
+      <c r="R292" t="s">
+        <v>31</v>
+      </c>
+      <c r="S292" t="s">
+        <v>31</v>
+      </c>
+      <c r="T292" t="s">
+        <v>31</v>
+      </c>
+      <c r="U292">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A292,B292,C292,D292,E292,F292,G292,H292,I292,J292,K292,L292,M292,N292,O292,P292,Q292,R292,S292,T292)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:21">
+      <c r="A293" t="b">
+        <v>1</v>
+      </c>
+      <c r="B293" t="s">
+        <v>26</v>
+      </c>
+      <c r="C293" t="s">
+        <v>191</v>
+      </c>
+      <c r="E293" t="s">
+        <v>38</v>
+      </c>
+      <c r="F293" t="s">
+        <v>27</v>
+      </c>
+      <c r="G293" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H293" t="s">
+        <v>29</v>
+      </c>
+      <c r="I293" t="s">
+        <v>83</v>
+      </c>
+      <c r="J293" t="s">
+        <v>41</v>
+      </c>
+      <c r="K293" t="s">
+        <v>31</v>
+      </c>
+      <c r="L293" t="s">
+        <v>32</v>
+      </c>
+      <c r="M293" t="s">
+        <v>31</v>
+      </c>
+      <c r="N293" t="s">
+        <v>31</v>
+      </c>
+      <c r="O293" t="s">
+        <v>31</v>
+      </c>
+      <c r="P293" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q293" t="s">
+        <v>31</v>
+      </c>
+      <c r="R293" t="s">
+        <v>31</v>
+      </c>
+      <c r="S293" t="s">
+        <v>31</v>
+      </c>
+      <c r="T293" t="s">
+        <v>31</v>
+      </c>
+      <c r="U293">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A293,B293,C293,D293,E293,F293,G293,H293,I293,J293,K293,L293,M293,N293,O293,P293,Q293,R293,S293,T293)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:21">
+      <c r="A294" t="b">
+        <v>1</v>
+      </c>
+      <c r="B294" t="s">
+        <v>26</v>
+      </c>
+      <c r="C294" t="s">
+        <v>192</v>
+      </c>
+      <c r="E294" t="s">
+        <v>38</v>
+      </c>
+      <c r="F294" t="s">
+        <v>27</v>
+      </c>
+      <c r="G294" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H294" t="s">
+        <v>29</v>
+      </c>
+      <c r="I294" t="s">
+        <v>83</v>
+      </c>
+      <c r="J294" t="s">
+        <v>41</v>
+      </c>
+      <c r="K294" t="s">
+        <v>31</v>
+      </c>
+      <c r="L294" t="s">
+        <v>32</v>
+      </c>
+      <c r="M294" t="s">
+        <v>31</v>
+      </c>
+      <c r="N294" t="s">
+        <v>31</v>
+      </c>
+      <c r="O294" t="s">
+        <v>31</v>
+      </c>
+      <c r="P294" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q294" t="s">
+        <v>31</v>
+      </c>
+      <c r="R294" t="s">
+        <v>31</v>
+      </c>
+      <c r="S294" t="s">
+        <v>31</v>
+      </c>
+      <c r="T294" t="s">
+        <v>31</v>
+      </c>
+      <c r="U294">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A294,B294,C294,D294,E294,F294,G294,H294,I294,J294,K294,L294,M294,N294,O294,P294,Q294,R294,S294,T294)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:21">
+      <c r="A295" t="b">
+        <v>1</v>
+      </c>
+      <c r="B295" t="s">
+        <v>26</v>
+      </c>
+      <c r="C295" t="s">
+        <v>151</v>
+      </c>
+      <c r="E295" t="s">
+        <v>38</v>
+      </c>
+      <c r="F295" t="s">
+        <v>27</v>
+      </c>
+      <c r="G295" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H295" t="s">
+        <v>29</v>
+      </c>
+      <c r="I295" t="s">
+        <v>83</v>
+      </c>
+      <c r="J295" t="s">
+        <v>41</v>
+      </c>
+      <c r="K295" t="s">
+        <v>31</v>
+      </c>
+      <c r="L295" t="s">
+        <v>32</v>
+      </c>
+      <c r="M295" t="s">
+        <v>212</v>
+      </c>
+      <c r="N295" t="str">
+        <f t="shared" si="6"/>
+        <v>113_540</v>
+      </c>
+      <c r="O295" t="s">
+        <v>31</v>
+      </c>
+      <c r="P295" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q295" t="s">
+        <v>31</v>
+      </c>
+      <c r="R295" t="s">
+        <v>31</v>
+      </c>
+      <c r="S295" t="s">
+        <v>31</v>
+      </c>
+      <c r="T295" t="s">
+        <v>31</v>
+      </c>
+      <c r="U295">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A295,B295,C295,D295,E295,F295,G295,H295,I295,J295,K295,L295,M295,N295,O295,P295,Q295,R295,S295,T295)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:21">
+      <c r="A296" t="b">
+        <v>1</v>
+      </c>
+      <c r="B296" t="s">
+        <v>26</v>
+      </c>
+      <c r="C296" t="s">
+        <v>163</v>
+      </c>
+      <c r="E296" t="s">
+        <v>38</v>
+      </c>
+      <c r="F296" t="s">
+        <v>27</v>
+      </c>
+      <c r="G296" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H296" t="s">
+        <v>29</v>
+      </c>
+      <c r="I296" t="s">
+        <v>83</v>
+      </c>
+      <c r="J296" t="s">
+        <v>41</v>
+      </c>
+      <c r="K296" t="s">
+        <v>31</v>
+      </c>
+      <c r="L296" t="s">
+        <v>32</v>
+      </c>
+      <c r="M296" t="s">
+        <v>213</v>
+      </c>
+      <c r="N296" t="str">
+        <f t="shared" si="6"/>
+        <v>111_595</v>
+      </c>
+      <c r="O296" t="s">
+        <v>31</v>
+      </c>
+      <c r="P296" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q296" t="s">
+        <v>31</v>
+      </c>
+      <c r="R296" t="s">
+        <v>31</v>
+      </c>
+      <c r="S296" t="s">
+        <v>31</v>
+      </c>
+      <c r="T296" t="s">
+        <v>31</v>
+      </c>
+      <c r="U296">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A296,B296,C296,D296,E296,F296,G296,H296,I296,J296,K296,L296,M296,N296,O296,P296,Q296,R296,S296,T296)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:21">
+      <c r="A297" t="b">
+        <v>1</v>
+      </c>
+      <c r="B297" t="s">
+        <v>26</v>
+      </c>
+      <c r="C297" t="s">
+        <v>168</v>
+      </c>
+      <c r="E297" t="s">
+        <v>38</v>
+      </c>
+      <c r="F297" t="s">
+        <v>27</v>
+      </c>
+      <c r="G297" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H297" t="s">
+        <v>29</v>
+      </c>
+      <c r="I297" t="s">
+        <v>83</v>
+      </c>
+      <c r="J297" t="s">
+        <v>41</v>
+      </c>
+      <c r="K297" t="s">
+        <v>31</v>
+      </c>
+      <c r="L297" t="s">
+        <v>32</v>
+      </c>
+      <c r="M297" t="s">
+        <v>213</v>
+      </c>
+      <c r="N297" t="str">
+        <f t="shared" si="6"/>
+        <v>213_595</v>
+      </c>
+      <c r="O297" t="s">
+        <v>31</v>
+      </c>
+      <c r="P297" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q297" t="s">
+        <v>31</v>
+      </c>
+      <c r="R297" t="s">
+        <v>31</v>
+      </c>
+      <c r="S297" t="s">
+        <v>31</v>
+      </c>
+      <c r="T297" t="s">
+        <v>31</v>
+      </c>
+      <c r="U297">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A297,B297,C297,D297,E297,F297,G297,H297,I297,J297,K297,L297,M297,N297,O297,P297,Q297,R297,S297,T297)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:21">
+      <c r="A298" t="b">
+        <v>1</v>
+      </c>
+      <c r="B298" t="s">
+        <v>26</v>
+      </c>
+      <c r="C298">
+        <v>909</v>
+      </c>
+      <c r="E298" t="s">
+        <v>38</v>
+      </c>
+      <c r="F298" t="s">
+        <v>27</v>
+      </c>
+      <c r="G298" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H298" t="s">
+        <v>29</v>
+      </c>
+      <c r="I298" t="s">
+        <v>83</v>
+      </c>
+      <c r="J298" t="s">
+        <v>41</v>
+      </c>
+      <c r="K298" t="s">
+        <v>31</v>
+      </c>
+      <c r="L298" t="s">
+        <v>32</v>
+      </c>
+      <c r="M298">
+        <v>950</v>
+      </c>
+      <c r="N298" t="str">
+        <f t="shared" si="6"/>
+        <v>909_950</v>
+      </c>
+      <c r="O298" t="s">
+        <v>31</v>
+      </c>
+      <c r="P298" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q298" t="s">
+        <v>31</v>
+      </c>
+      <c r="R298" t="s">
+        <v>31</v>
+      </c>
+      <c r="S298" t="s">
+        <v>31</v>
+      </c>
+      <c r="T298" t="s">
+        <v>31</v>
+      </c>
+      <c r="U298">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A298,B298,C298,D298,E298,F298,G298,H298,I298,J298,K298,L298,M298,N298,O298,P298,Q298,R298,S298,T298)</f>
+        <v>-547339</v>
+      </c>
+    </row>
+    <row r="299" spans="1:21">
+      <c r="A299" t="b">
+        <v>1</v>
+      </c>
+      <c r="B299" t="s">
+        <v>26</v>
+      </c>
+      <c r="C299">
+        <v>900</v>
+      </c>
+      <c r="E299" t="s">
+        <v>38</v>
+      </c>
+      <c r="F299" t="s">
+        <v>27</v>
+      </c>
+      <c r="G299" t="str">
+        <f>INDEX('User Inputs'!$G$3:$G$14,MATCH(1,'User Inputs'!$J$3:$J$14,0))</f>
+        <v>2026M05</v>
+      </c>
+      <c r="H299" t="s">
+        <v>29</v>
+      </c>
+      <c r="I299" t="s">
+        <v>83</v>
+      </c>
+      <c r="J299" t="s">
+        <v>41</v>
+      </c>
+      <c r="K299" t="s">
+        <v>31</v>
+      </c>
+      <c r="L299" t="s">
+        <v>32</v>
+      </c>
+      <c r="M299">
+        <v>965</v>
+      </c>
+      <c r="N299" t="str">
+        <f t="shared" si="6"/>
+        <v>900_965</v>
+      </c>
+      <c r="O299" t="s">
+        <v>31</v>
+      </c>
+      <c r="P299" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q299" t="s">
+        <v>31</v>
+      </c>
+      <c r="R299" t="s">
+        <v>31</v>
+      </c>
+      <c r="S299" t="s">
+        <v>31</v>
+      </c>
+      <c r="T299" t="s">
+        <v>31</v>
+      </c>
+      <c r="U299">
+        <f>_xll.OneStreamExcelAddIn.XFFunctions.XFGetCell(A299,B299,C299,D299,E299,F299,G299,H299,I299,J299,K299,L299,M299,N299,O299,P299,Q299,R299,S299,T299)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U98">
     <sortCondition ref="I1:I98"/>
@@ -16751,7 +22047,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AC87DD-3C9C-4AAA-90BE-5F1A64C92E6B}">
-  <dimension ref="A1:J237"/>
+  <dimension ref="A1:J240"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -23351,7 +28647,7 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="12" t="str">
-        <f t="shared" ref="A195:A237" si="3">_xlfn.CONCAT(B195,"-",C195,D195,E195)</f>
+        <f t="shared" ref="A195:A240" si="3">_xlfn.CONCAT(B195,"-",C195,D195,E195)</f>
         <v>111-172611020330330</v>
       </c>
       <c r="B195">
@@ -24811,6 +30107,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="238" spans="1:8">
+      <c r="A238" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>111-170SACADV0</v>
+      </c>
+      <c r="B238">
+        <v>111</v>
+      </c>
+      <c r="C238">
+        <v>170</v>
+      </c>
+      <c r="D238" t="s">
+        <v>178</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238" t="str">
+        <f>INDEX('User Inputs'!$I$3:$I$14,MATCH('OneStream Pulls'!G238,'User Inputs'!$G$3:$G$14,0))</f>
+        <v>May</v>
+      </c>
+      <c r="G238" t="str">
+        <f>LEFT('OneStream Pulls'!G238,4)</f>
+        <v>2026</v>
+      </c>
+      <c r="H238">
+        <f>SUM('OneStream Pulls'!U238:U262)</f>
+        <v>378772.66</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8">
+      <c r="A239" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>111-170SACADV2</v>
+      </c>
+      <c r="B239">
+        <v>111</v>
+      </c>
+      <c r="C239">
+        <v>170</v>
+      </c>
+      <c r="D239" t="s">
+        <v>178</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+      <c r="F239" t="str">
+        <f>INDEX('User Inputs'!$I$3:$I$14,MATCH('OneStream Pulls'!G239,'User Inputs'!$G$3:$G$14,0))</f>
+        <v>May</v>
+      </c>
+      <c r="G239" t="str">
+        <f>LEFT('OneStream Pulls'!G239,4)</f>
+        <v>2026</v>
+      </c>
+      <c r="H239">
+        <f>SUM('OneStream Pulls'!U263:U270)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8">
+      <c r="A240" s="12" t="str">
+        <f t="shared" si="3"/>
+        <v>111-170SACADV1</v>
+      </c>
+      <c r="B240">
+        <v>111</v>
+      </c>
+      <c r="C240">
+        <v>170</v>
+      </c>
+      <c r="D240" t="s">
+        <v>178</v>
+      </c>
+      <c r="E240">
+        <v>1</v>
+      </c>
+      <c r="F240" t="str">
+        <f>INDEX('User Inputs'!$I$3:$I$14,MATCH('OneStream Pulls'!G240,'User Inputs'!$G$3:$G$14,0))</f>
+        <v>May</v>
+      </c>
+      <c r="G240" t="str">
+        <f>LEFT('OneStream Pulls'!G240,4)</f>
+        <v>2026</v>
+      </c>
+      <c r="H240">
+        <f>SUM('OneStream Pulls'!U271:U299)</f>
+        <v>5142.2800000000279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
